--- a/tests/trj/Example_CEM/Example_output_files/PSD_Plot.xlsx
+++ b/tests/trj/Example_CEM/Example_output_files/PSD_Plot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42c400a6d2268350/Penn/GitHub/PARSE/tests/trj/Example_CEM/Example_output_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{443F72C7-0366-44FC-9683-A58BD3105D20}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF1A2AE2-9C71-4DC5-BEAD-11FF805E3095}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GRO-GRO" sheetId="1" r:id="rId1"/>
@@ -2519,220 +2519,220 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.22240000000000068</c:v>
+                  <c:v>0.21319999999999811</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.64480000000000037</c:v>
+                  <c:v>0.62480000000000258</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74240000000000017</c:v>
+                  <c:v>0.69999999999999774</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.81199999999999872</c:v>
+                  <c:v>0.77320000000000211</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.80439999999999778</c:v>
+                  <c:v>0.78799999999999693</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.84000000000000186</c:v>
+                  <c:v>0.79120000000000179</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.76119999999999899</c:v>
+                  <c:v>0.78679999999999795</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80800000000000094</c:v>
+                  <c:v>0.77880000000000049</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.81240000000000134</c:v>
+                  <c:v>0.79719999999999946</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.77079999999999527</c:v>
+                  <c:v>0.80440000000000222</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.80360000000000142</c:v>
+                  <c:v>0.81919999999999693</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82240000000000379</c:v>
+                  <c:v>0.79120000000000357</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.77159999999999607</c:v>
+                  <c:v>0.80760000000000098</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.72960000000000069</c:v>
+                  <c:v>0.75359999999999805</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.77079999999999971</c:v>
+                  <c:v>0.77160000000000051</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.74240000000000017</c:v>
+                  <c:v>0.79119999999999568</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.84000000000000374</c:v>
+                  <c:v>0.86800000000000521</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.75519999999999965</c:v>
+                  <c:v>0.82199999999999751</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.87319999999999987</c:v>
+                  <c:v>0.85079999999999967</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.80439999999999778</c:v>
+                  <c:v>0.83519999999999961</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.84439999999999771</c:v>
+                  <c:v>0.83600000000000041</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.88360000000000527</c:v>
+                  <c:v>0.84200000000000352</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8775999999999976</c:v>
+                  <c:v>0.76799999999999913</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.85560000000000003</c:v>
+                  <c:v>0.802399999999998</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.81039999999999712</c:v>
+                  <c:v>0.78879999999999773</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.84240000000000015</c:v>
+                  <c:v>0.90840000000000176</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.78520000000000423</c:v>
+                  <c:v>0.85600000000000198</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.0051999999999941</c:v>
+                  <c:v>0.9955999999999956</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.8432000000000025</c:v>
+                  <c:v>0.88960000000000239</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.85120000000000384</c:v>
+                  <c:v>0.88520000000000465</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.82719999999999461</c:v>
+                  <c:v>0.76239999999999453</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.7532000000000032</c:v>
+                  <c:v>0.85160000000000424</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.76399999999999613</c:v>
+                  <c:v>0.68759999999999566</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.68840000000000257</c:v>
+                  <c:v>0.68440000000000301</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.77360000000000151</c:v>
+                  <c:v>0.61800000000000077</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.70999999999999797</c:v>
+                  <c:v>0.66919999999999735</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.76720000000000177</c:v>
+                  <c:v>0.71680000000000221</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.431999999999999</c:v>
+                  <c:v>0.65279999999999661</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.61080000000000134</c:v>
+                  <c:v>0.64600000000000224</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.58560000000000156</c:v>
+                  <c:v>0.60880000000000256</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.621999999999997</c:v>
+                  <c:v>0.58999999999999631</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.91720000000000346</c:v>
+                  <c:v>0.75880000000000325</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.61959999999999682</c:v>
+                  <c:v>0.65679999999999605</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.49080000000000185</c:v>
+                  <c:v>0.54040000000000166</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.65200000000000158</c:v>
+                  <c:v>0.54640000000000211</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.44399999999999756</c:v>
+                  <c:v>0.52079999999999738</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.33280000000000204</c:v>
+                  <c:v>0.46960000000000168</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.57679999999999643</c:v>
+                  <c:v>0.55159999999999698</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.45320000000000132</c:v>
+                  <c:v>0.73160000000000258</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.63520000000000243</c:v>
+                  <c:v>0.48760000000000142</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.12799999999999909</c:v>
+                  <c:v>0.18759999999999899</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.33840000000000459</c:v>
+                  <c:v>0.20960000000000295</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.18879999999999908</c:v>
+                  <c:v>0.21319999999999892</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.3016000000000007</c:v>
+                  <c:v>0.24960000000000071</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1731999999999991</c:v>
+                  <c:v>0.30119999999999847</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.29360000000000103</c:v>
+                  <c:v>0.29840000000000111</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.69960000000000266</c:v>
+                  <c:v>0.40800000000000147</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.34479999999999811</c:v>
+                  <c:v>0.24959999999999849</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>6.120000000000022E-2</c:v>
+                  <c:v>0.28560000000000102</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>3.6799999999999694E-2</c:v>
+                  <c:v>4.5199999999999858E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>3.6400000000000175E-2</c:v>
+                  <c:v>4.2800000000000074E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>9.2000000000000744E-3</c:v>
+                  <c:v>2.9600000000000147E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>4.5999999999999687E-2</c:v>
+                  <c:v>4.799999999999973E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>5.0400000000000209E-2</c:v>
+                  <c:v>6.3200000000000145E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>6.9199999999999581E-2</c:v>
+                  <c:v>5.679999999999974E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>3.4800000000000234E-2</c:v>
+                  <c:v>7.0800000000000279E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>8.6400000000000254E-2</c:v>
+                  <c:v>4.2800000000000074E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.10120000000000033</c:v>
+                  <c:v>0.12560000000000054</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.61439999999999129</c:v>
+                  <c:v>0.2663999999999962</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0</c:v>
+                  <c:v>7.600000000000029E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0</c:v>
+                  <c:v>0.15560000000000054</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0</c:v>
+                  <c:v>8.3200000000000288E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4806,214 +4806,214 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.99458999999999997</c:v>
+                  <c:v>0.99451999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.97867999999999999</c:v>
+                  <c:v>0.97884000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.96057000000000003</c:v>
+                  <c:v>0.96077000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.94106999999999996</c:v>
+                  <c:v>0.94137000000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.92081000000000002</c:v>
+                  <c:v>0.92098000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.90036000000000005</c:v>
+                  <c:v>0.90049000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.87960000000000005</c:v>
+                  <c:v>0.87983</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.85873999999999995</c:v>
+                  <c:v>0.85919000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.83789999999999998</c:v>
+                  <c:v>0.83831999999999995</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.81620000000000004</c:v>
+                  <c:v>0.81684999999999997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.79430999999999996</c:v>
+                  <c:v>0.79527999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.77329000000000003</c:v>
+                  <c:v>0.77385999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.75244999999999995</c:v>
+                  <c:v>0.75261</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.73068</c:v>
+                  <c:v>0.73133000000000004</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.70828000000000002</c:v>
+                  <c:v>0.70909</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.68652999999999997</c:v>
+                  <c:v>0.68732000000000004</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.66439999999999999</c:v>
+                  <c:v>0.66598999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.64183999999999997</c:v>
+                  <c:v>0.64359999999999995</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.61999000000000004</c:v>
+                  <c:v>0.62207000000000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.59782999999999997</c:v>
+                  <c:v>0.59884000000000004</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.57533999999999996</c:v>
+                  <c:v>0.57691999999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.55220000000000002</c:v>
+                  <c:v>0.55462</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.53008999999999995</c:v>
+                  <c:v>0.53288000000000002</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.50912999999999997</c:v>
+                  <c:v>0.51078999999999997</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.48691000000000001</c:v>
+                  <c:v>0.48836000000000002</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.46562999999999999</c:v>
+                  <c:v>0.46644000000000002</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.44438</c:v>
+                  <c:v>0.44485000000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.42377999999999999</c:v>
+                  <c:v>0.42449999999999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.40337000000000001</c:v>
+                  <c:v>0.40405000000000002</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.38228000000000001</c:v>
+                  <c:v>0.38413999999999998</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.36359999999999998</c:v>
+                  <c:v>0.36514999999999997</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.34447</c:v>
+                  <c:v>0.34588999999999998</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.32571</c:v>
+                  <c:v>0.32683000000000001</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.30769999999999997</c:v>
+                  <c:v>0.30853000000000003</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.29013</c:v>
+                  <c:v>0.28928999999999999</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.27145999999999998</c:v>
+                  <c:v>0.27139999999999997</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.25273000000000001</c:v>
+                  <c:v>0.25509999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.23733000000000001</c:v>
+                  <c:v>0.23845</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.22248999999999999</c:v>
+                  <c:v>0.22289</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.20765</c:v>
+                  <c:v>0.20718</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.19286</c:v>
+                  <c:v>0.19419</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.17979999999999999</c:v>
+                  <c:v>0.18040999999999999</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.16800000000000001</c:v>
+                  <c:v>0.16939000000000001</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.15620999999999999</c:v>
+                  <c:v>0.15767</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.14399999999999999</c:v>
+                  <c:v>0.14473</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.13511999999999999</c:v>
+                  <c:v>0.13481000000000001</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.12418999999999999</c:v>
+                  <c:v>0.12586</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.11550000000000001</c:v>
+                  <c:v>0.11734</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.10788</c:v>
+                  <c:v>0.10847</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>9.9580000000000002E-2</c:v>
+                  <c:v>9.9299999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>9.0980000000000005E-2</c:v>
+                  <c:v>9.2149999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>8.4669999999999995E-2</c:v>
+                  <c:v>8.4699999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>7.6259999999999994E-2</c:v>
+                  <c:v>7.5319999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>6.7750000000000005E-2</c:v>
+                  <c:v>6.9019999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>6.021E-2</c:v>
+                  <c:v>6.2330000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>5.4120000000000001E-2</c:v>
+                  <c:v>5.3839999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4.6339999999999999E-2</c:v>
+                  <c:v>4.6780000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>3.9129999999999998E-2</c:v>
+                  <c:v>4.0989999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>3.3599999999999998E-2</c:v>
+                  <c:v>3.388E-2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2.6270000000000002E-2</c:v>
+                  <c:v>2.8080000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>2.2790000000000001E-2</c:v>
+                  <c:v>2.4080000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>1.753E-2</c:v>
+                  <c:v>1.7909999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>1.3129999999999999E-2</c:v>
+                  <c:v>1.325E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>8.6700000000000006E-3</c:v>
+                  <c:v>7.4900000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>5.2399999999999999E-3</c:v>
+                  <c:v>6.6499999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>4.2100000000000002E-3</c:v>
+                  <c:v>5.6100000000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>2.8700000000000002E-3</c:v>
+                  <c:v>2.96E-3</c:v>
                 </c:pt>
                 <c:pt idx="69">
+                  <c:v>2.2799999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>1.6800000000000001E-3</c:v>
                 </c:pt>
-                <c:pt idx="70">
-                  <c:v>1.2800000000000001E-3</c:v>
-                </c:pt>
                 <c:pt idx="71">
-                  <c:v>6.4000000000000005E-4</c:v>
+                  <c:v>6.6E-4</c:v>
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>0</c:v>
@@ -5327,217 +5327,217 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21640000000000131</c:v>
+                  <c:v>0.21920000000000192</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.63639999999999863</c:v>
+                  <c:v>0.62719999999999609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.72439999999999771</c:v>
+                  <c:v>0.72280000000000055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78000000000000225</c:v>
+                  <c:v>0.77599999999999825</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81039999999999712</c:v>
+                  <c:v>0.81559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.81799999999999984</c:v>
+                  <c:v>0.81960000000000144</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83039999999999925</c:v>
+                  <c:v>0.82639999999999969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.83440000000000514</c:v>
+                  <c:v>0.82560000000000078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.83359999999999801</c:v>
+                  <c:v>0.83480000000000143</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.86799999999999689</c:v>
+                  <c:v>0.85879999999999879</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.87560000000000227</c:v>
+                  <c:v>0.86279999999999835</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.8408000000000001</c:v>
+                  <c:v>0.85680000000000278</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.83360000000000245</c:v>
+                  <c:v>0.84999999999999887</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.85119999999999785</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.88960000000000072</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.87079999999999746</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.89599999999999824</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.87000000000000111</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.88520000000000243</c:v>
+                  <c:v>0.85320000000000584</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9024000000000002</c:v>
+                  <c:v>0.89560000000000006</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.87399999999999622</c:v>
+                  <c:v>0.86119999999999675</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.88640000000000196</c:v>
+                  <c:v>0.92919999999999814</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.89959999999999962</c:v>
+                  <c:v>0.87680000000000125</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.92560000000000087</c:v>
+                  <c:v>0.89200000000000268</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.88440000000000218</c:v>
+                  <c:v>0.86959999999999849</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.83839999999999837</c:v>
+                  <c:v>0.88360000000000138</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.8887999999999977</c:v>
+                  <c:v>0.89719999999999722</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85120000000000007</c:v>
+                  <c:v>0.87679999999999902</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.85000000000000264</c:v>
+                  <c:v>0.86360000000000303</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82399999999999585</c:v>
+                  <c:v>0.81399999999999706</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.81640000000000224</c:v>
+                  <c:v>0.81800000000000161</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.8436000000000029</c:v>
+                  <c:v>0.79640000000000433</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.7471999999999972</c:v>
+                  <c:v>0.75959999999999628</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.76520000000000188</c:v>
+                  <c:v>0.77040000000000275</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.75039999999999596</c:v>
+                  <c:v>0.76239999999999453</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.72040000000000359</c:v>
+                  <c:v>0.73200000000000187</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.70280000000000142</c:v>
+                  <c:v>0.76960000000000417</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7467999999999968</c:v>
+                  <c:v>0.71559999999999691</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.74920000000000142</c:v>
+                  <c:v>0.65200000000000158</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.61599999999999655</c:v>
+                  <c:v>0.66599999999999637</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.5936000000000029</c:v>
+                  <c:v>0.62240000000000184</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.59360000000000179</c:v>
+                  <c:v>0.62840000000000229</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.5915999999999968</c:v>
+                  <c:v>0.51959999999999729</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.52240000000000253</c:v>
+                  <c:v>0.55120000000000258</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.47199999999999659</c:v>
+                  <c:v>0.44079999999999664</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.47160000000000257</c:v>
+                  <c:v>0.46880000000000199</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.48840000000000167</c:v>
+                  <c:v>0.51760000000000217</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.35519999999999807</c:v>
+                  <c:v>0.39679999999999727</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.43720000000000137</c:v>
+                  <c:v>0.35800000000000182</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.34759999999999774</c:v>
+                  <c:v>0.34079999999999816</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.30480000000000118</c:v>
+                  <c:v>0.35480000000000139</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.33200000000000124</c:v>
+                  <c:v>0.36680000000000118</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.34399999999999803</c:v>
+                  <c:v>0.28599999999999864</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.25240000000000357</c:v>
+                  <c:v>0.29800000000000365</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.33639999999999826</c:v>
+                  <c:v>0.37519999999999798</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.34040000000000081</c:v>
+                  <c:v>0.25200000000000089</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.30159999999999859</c:v>
+                  <c:v>0.26759999999999834</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.24360000000000079</c:v>
+                  <c:v>0.3396000000000014</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.3112000000000012</c:v>
+                  <c:v>0.28240000000000087</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.28839999999999849</c:v>
+                  <c:v>0.23159999999999892</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.22120000000000078</c:v>
+                  <c:v>0.28440000000000093</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.2931999999999983</c:v>
+                  <c:v>0.23199999999999874</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.13920000000000052</c:v>
+                  <c:v>0.16000000000000056</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.21040000000000078</c:v>
+                  <c:v>0.24680000000000096</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1759999999999991</c:v>
+                  <c:v>0.18639999999999898</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.17840000000000059</c:v>
+                  <c:v>0.2304000000000008</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.13719999999999929</c:v>
+                  <c:v>3.3599999999999838E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>4.1200000000000132E-2</c:v>
+                  <c:v>4.1600000000000116E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>5.3600000000000189E-2</c:v>
+                  <c:v>0.1060000000000004</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>4.760000000000017E-2</c:v>
+                  <c:v>2.7200000000000099E-2</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1.5999999999999771E-2</c:v>
+                  <c:v>2.3999999999999654E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2.5600000000000091E-2</c:v>
+                  <c:v>4.0800000000000149E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2.5600000000000091E-2</c:v>
+                  <c:v>2.6400000000000094E-2</c:v>
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0</c:v>
@@ -6302,217 +6302,217 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21640000000000131</c:v>
+                  <c:v>0.21920000000000192</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.63639999999999863</c:v>
+                  <c:v>0.62719999999999609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.72439999999999771</c:v>
+                  <c:v>0.72280000000000055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78000000000000225</c:v>
+                  <c:v>0.77599999999999825</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81039999999999712</c:v>
+                  <c:v>0.81559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.81799999999999984</c:v>
+                  <c:v>0.81960000000000144</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83039999999999925</c:v>
+                  <c:v>0.82639999999999969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.83440000000000514</c:v>
+                  <c:v>0.82560000000000078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.83359999999999801</c:v>
+                  <c:v>0.83480000000000143</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.86799999999999689</c:v>
+                  <c:v>0.85879999999999879</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.87560000000000227</c:v>
+                  <c:v>0.86279999999999835</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.8408000000000001</c:v>
+                  <c:v>0.85680000000000278</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.83360000000000245</c:v>
+                  <c:v>0.84999999999999887</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.85119999999999785</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.88960000000000072</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.87079999999999746</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.89599999999999824</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.87000000000000111</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.88520000000000243</c:v>
+                  <c:v>0.85320000000000584</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9024000000000002</c:v>
+                  <c:v>0.89560000000000006</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.87399999999999622</c:v>
+                  <c:v>0.86119999999999675</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.88640000000000196</c:v>
+                  <c:v>0.92919999999999814</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.89959999999999962</c:v>
+                  <c:v>0.87680000000000125</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.92560000000000087</c:v>
+                  <c:v>0.89200000000000268</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.88440000000000218</c:v>
+                  <c:v>0.86959999999999849</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.83839999999999837</c:v>
+                  <c:v>0.88360000000000138</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.8887999999999977</c:v>
+                  <c:v>0.89719999999999722</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85120000000000007</c:v>
+                  <c:v>0.87679999999999902</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.85000000000000264</c:v>
+                  <c:v>0.86360000000000303</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82399999999999585</c:v>
+                  <c:v>0.81399999999999706</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.81640000000000224</c:v>
+                  <c:v>0.81800000000000161</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.8436000000000029</c:v>
+                  <c:v>0.79640000000000433</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.7471999999999972</c:v>
+                  <c:v>0.75959999999999628</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.76520000000000188</c:v>
+                  <c:v>0.77040000000000275</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.75039999999999596</c:v>
+                  <c:v>0.76239999999999453</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.72040000000000359</c:v>
+                  <c:v>0.73200000000000187</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.70280000000000142</c:v>
+                  <c:v>0.76960000000000417</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7467999999999968</c:v>
+                  <c:v>0.71559999999999691</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.74920000000000142</c:v>
+                  <c:v>0.65200000000000158</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.61599999999999655</c:v>
+                  <c:v>0.66599999999999637</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.5936000000000029</c:v>
+                  <c:v>0.62240000000000184</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.59360000000000179</c:v>
+                  <c:v>0.62840000000000229</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.5915999999999968</c:v>
+                  <c:v>0.51959999999999729</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.52240000000000253</c:v>
+                  <c:v>0.55120000000000258</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.47199999999999659</c:v>
+                  <c:v>0.44079999999999664</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.47160000000000257</c:v>
+                  <c:v>0.46880000000000199</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.48840000000000167</c:v>
+                  <c:v>0.51760000000000217</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.35519999999999807</c:v>
+                  <c:v>0.39679999999999727</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.43720000000000137</c:v>
+                  <c:v>0.35800000000000182</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.34759999999999774</c:v>
+                  <c:v>0.34079999999999816</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.30480000000000118</c:v>
+                  <c:v>0.35480000000000139</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.33200000000000124</c:v>
+                  <c:v>0.36680000000000118</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.34399999999999803</c:v>
+                  <c:v>0.28599999999999864</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.25240000000000357</c:v>
+                  <c:v>0.29800000000000365</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.33639999999999826</c:v>
+                  <c:v>0.37519999999999798</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.34040000000000081</c:v>
+                  <c:v>0.25200000000000089</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.30159999999999859</c:v>
+                  <c:v>0.26759999999999834</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.24360000000000079</c:v>
+                  <c:v>0.3396000000000014</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.3112000000000012</c:v>
+                  <c:v>0.28240000000000087</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.28839999999999849</c:v>
+                  <c:v>0.23159999999999892</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.22120000000000078</c:v>
+                  <c:v>0.28440000000000093</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.2931999999999983</c:v>
+                  <c:v>0.23199999999999874</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.13920000000000052</c:v>
+                  <c:v>0.16000000000000056</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.21040000000000078</c:v>
+                  <c:v>0.24680000000000096</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1759999999999991</c:v>
+                  <c:v>0.18639999999999898</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.17840000000000059</c:v>
+                  <c:v>0.2304000000000008</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.13719999999999929</c:v>
+                  <c:v>3.3599999999999838E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>4.1200000000000132E-2</c:v>
+                  <c:v>4.1600000000000116E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>5.3600000000000189E-2</c:v>
+                  <c:v>0.1060000000000004</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>4.760000000000017E-2</c:v>
+                  <c:v>2.7200000000000099E-2</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1.5999999999999771E-2</c:v>
+                  <c:v>2.3999999999999654E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2.5600000000000091E-2</c:v>
+                  <c:v>4.0800000000000149E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2.5600000000000091E-2</c:v>
+                  <c:v>2.6400000000000094E-2</c:v>
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0</c:v>
@@ -7316,220 +7316,220 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.22240000000000068</c:v>
+                  <c:v>0.21319999999999811</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.64480000000000037</c:v>
+                  <c:v>0.62480000000000258</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74240000000000017</c:v>
+                  <c:v>0.69999999999999774</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.81199999999999872</c:v>
+                  <c:v>0.77320000000000211</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.80439999999999778</c:v>
+                  <c:v>0.78799999999999693</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.84000000000000186</c:v>
+                  <c:v>0.79120000000000179</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.76119999999999899</c:v>
+                  <c:v>0.78679999999999795</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80800000000000094</c:v>
+                  <c:v>0.77880000000000049</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.81240000000000134</c:v>
+                  <c:v>0.79719999999999946</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.77079999999999527</c:v>
+                  <c:v>0.80440000000000222</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.80360000000000142</c:v>
+                  <c:v>0.81919999999999693</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82240000000000379</c:v>
+                  <c:v>0.79120000000000357</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.77159999999999607</c:v>
+                  <c:v>0.80760000000000098</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.72960000000000069</c:v>
+                  <c:v>0.75359999999999805</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.77079999999999971</c:v>
+                  <c:v>0.77160000000000051</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.74240000000000017</c:v>
+                  <c:v>0.79119999999999568</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.84000000000000374</c:v>
+                  <c:v>0.86800000000000521</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.75519999999999965</c:v>
+                  <c:v>0.82199999999999751</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.87319999999999987</c:v>
+                  <c:v>0.85079999999999967</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.80439999999999778</c:v>
+                  <c:v>0.83519999999999961</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.84439999999999771</c:v>
+                  <c:v>0.83600000000000041</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.88360000000000527</c:v>
+                  <c:v>0.84200000000000352</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8775999999999976</c:v>
+                  <c:v>0.76799999999999913</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.85560000000000003</c:v>
+                  <c:v>0.802399999999998</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.81039999999999712</c:v>
+                  <c:v>0.78879999999999773</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.84240000000000015</c:v>
+                  <c:v>0.90840000000000176</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.78520000000000423</c:v>
+                  <c:v>0.85600000000000198</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.0051999999999941</c:v>
+                  <c:v>0.9955999999999956</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.8432000000000025</c:v>
+                  <c:v>0.88960000000000239</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.85120000000000384</c:v>
+                  <c:v>0.88520000000000465</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.82719999999999461</c:v>
+                  <c:v>0.76239999999999453</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.7532000000000032</c:v>
+                  <c:v>0.85160000000000424</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.76399999999999613</c:v>
+                  <c:v>0.68759999999999566</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.68840000000000257</c:v>
+                  <c:v>0.68440000000000301</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.77360000000000151</c:v>
+                  <c:v>0.61800000000000077</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.70999999999999797</c:v>
+                  <c:v>0.66919999999999735</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.76720000000000177</c:v>
+                  <c:v>0.71680000000000221</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.431999999999999</c:v>
+                  <c:v>0.65279999999999661</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.61080000000000134</c:v>
+                  <c:v>0.64600000000000224</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.58560000000000156</c:v>
+                  <c:v>0.60880000000000256</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.621999999999997</c:v>
+                  <c:v>0.58999999999999631</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.91720000000000346</c:v>
+                  <c:v>0.75880000000000325</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.61959999999999682</c:v>
+                  <c:v>0.65679999999999605</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.49080000000000185</c:v>
+                  <c:v>0.54040000000000166</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.65200000000000158</c:v>
+                  <c:v>0.54640000000000211</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.44399999999999756</c:v>
+                  <c:v>0.52079999999999738</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.33280000000000204</c:v>
+                  <c:v>0.46960000000000168</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.57679999999999643</c:v>
+                  <c:v>0.55159999999999698</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.45320000000000132</c:v>
+                  <c:v>0.73160000000000258</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.63520000000000243</c:v>
+                  <c:v>0.48760000000000142</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.12799999999999909</c:v>
+                  <c:v>0.18759999999999899</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.33840000000000459</c:v>
+                  <c:v>0.20960000000000295</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.18879999999999908</c:v>
+                  <c:v>0.21319999999999892</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.3016000000000007</c:v>
+                  <c:v>0.24960000000000071</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1731999999999991</c:v>
+                  <c:v>0.30119999999999847</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.29360000000000103</c:v>
+                  <c:v>0.29840000000000111</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.69960000000000266</c:v>
+                  <c:v>0.40800000000000147</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.34479999999999811</c:v>
+                  <c:v>0.24959999999999849</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>6.120000000000022E-2</c:v>
+                  <c:v>0.28560000000000102</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>3.6799999999999694E-2</c:v>
+                  <c:v>4.5199999999999858E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>3.6400000000000175E-2</c:v>
+                  <c:v>4.2800000000000074E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>9.2000000000000744E-3</c:v>
+                  <c:v>2.9600000000000147E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>4.5999999999999687E-2</c:v>
+                  <c:v>4.799999999999973E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>5.0400000000000209E-2</c:v>
+                  <c:v>6.3200000000000145E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>6.9199999999999581E-2</c:v>
+                  <c:v>5.679999999999974E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>3.4800000000000234E-2</c:v>
+                  <c:v>7.0800000000000279E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>8.6400000000000254E-2</c:v>
+                  <c:v>4.2800000000000074E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.10120000000000033</c:v>
+                  <c:v>0.12560000000000054</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.61439999999999129</c:v>
+                  <c:v>0.2663999999999962</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0</c:v>
+                  <c:v>7.600000000000029E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0</c:v>
+                  <c:v>0.15560000000000054</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0</c:v>
+                  <c:v>8.3200000000000288E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8221,217 +8221,217 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21640000000000131</c:v>
+                  <c:v>0.21920000000000192</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.63639999999999863</c:v>
+                  <c:v>0.62719999999999609</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.72439999999999771</c:v>
+                  <c:v>0.72280000000000055</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78000000000000225</c:v>
+                  <c:v>0.77599999999999825</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.81039999999999712</c:v>
+                  <c:v>0.81559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.81799999999999984</c:v>
+                  <c:v>0.81960000000000144</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.83039999999999925</c:v>
+                  <c:v>0.82639999999999969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.83440000000000514</c:v>
+                  <c:v>0.82560000000000078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.83359999999999801</c:v>
+                  <c:v>0.83480000000000143</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.86799999999999689</c:v>
+                  <c:v>0.85879999999999879</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.87560000000000227</c:v>
+                  <c:v>0.86279999999999835</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.8408000000000001</c:v>
+                  <c:v>0.85680000000000278</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.83360000000000245</c:v>
+                  <c:v>0.84999999999999887</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0.85119999999999785</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.88960000000000072</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.87079999999999746</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.89599999999999824</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.87000000000000111</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.88520000000000243</c:v>
+                  <c:v>0.85320000000000584</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9024000000000002</c:v>
+                  <c:v>0.89560000000000006</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.87399999999999622</c:v>
+                  <c:v>0.86119999999999675</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.88640000000000196</c:v>
+                  <c:v>0.92919999999999814</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.89959999999999962</c:v>
+                  <c:v>0.87680000000000125</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.92560000000000087</c:v>
+                  <c:v>0.89200000000000268</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.88440000000000218</c:v>
+                  <c:v>0.86959999999999849</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.83839999999999837</c:v>
+                  <c:v>0.88360000000000138</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.8887999999999977</c:v>
+                  <c:v>0.89719999999999722</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85120000000000007</c:v>
+                  <c:v>0.87679999999999902</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.85000000000000264</c:v>
+                  <c:v>0.86360000000000303</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82399999999999585</c:v>
+                  <c:v>0.81399999999999706</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.81640000000000224</c:v>
+                  <c:v>0.81800000000000161</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.8436000000000029</c:v>
+                  <c:v>0.79640000000000433</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.7471999999999972</c:v>
+                  <c:v>0.75959999999999628</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.76520000000000188</c:v>
+                  <c:v>0.77040000000000275</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.75039999999999596</c:v>
+                  <c:v>0.76239999999999453</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.72040000000000359</c:v>
+                  <c:v>0.73200000000000187</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.70280000000000142</c:v>
+                  <c:v>0.76960000000000417</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7467999999999968</c:v>
+                  <c:v>0.71559999999999691</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.74920000000000142</c:v>
+                  <c:v>0.65200000000000158</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.61599999999999655</c:v>
+                  <c:v>0.66599999999999637</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.5936000000000029</c:v>
+                  <c:v>0.62240000000000184</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.59360000000000179</c:v>
+                  <c:v>0.62840000000000229</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.5915999999999968</c:v>
+                  <c:v>0.51959999999999729</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.52240000000000253</c:v>
+                  <c:v>0.55120000000000258</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.47199999999999659</c:v>
+                  <c:v>0.44079999999999664</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.47160000000000257</c:v>
+                  <c:v>0.46880000000000199</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.48840000000000167</c:v>
+                  <c:v>0.51760000000000217</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.35519999999999807</c:v>
+                  <c:v>0.39679999999999727</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.43720000000000137</c:v>
+                  <c:v>0.35800000000000182</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.34759999999999774</c:v>
+                  <c:v>0.34079999999999816</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.30480000000000118</c:v>
+                  <c:v>0.35480000000000139</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.33200000000000124</c:v>
+                  <c:v>0.36680000000000118</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.34399999999999803</c:v>
+                  <c:v>0.28599999999999864</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.25240000000000357</c:v>
+                  <c:v>0.29800000000000365</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.33639999999999826</c:v>
+                  <c:v>0.37519999999999798</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.34040000000000081</c:v>
+                  <c:v>0.25200000000000089</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.30159999999999859</c:v>
+                  <c:v>0.26759999999999834</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.24360000000000079</c:v>
+                  <c:v>0.3396000000000014</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.3112000000000012</c:v>
+                  <c:v>0.28240000000000087</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.28839999999999849</c:v>
+                  <c:v>0.23159999999999892</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.22120000000000078</c:v>
+                  <c:v>0.28440000000000093</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.2931999999999983</c:v>
+                  <c:v>0.23199999999999874</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.13920000000000052</c:v>
+                  <c:v>0.16000000000000056</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.21040000000000078</c:v>
+                  <c:v>0.24680000000000096</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.1759999999999991</c:v>
+                  <c:v>0.18639999999999898</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.17840000000000059</c:v>
+                  <c:v>0.2304000000000008</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.13719999999999929</c:v>
+                  <c:v>3.3599999999999838E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>4.1200000000000132E-2</c:v>
+                  <c:v>4.1600000000000116E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>5.3600000000000189E-2</c:v>
+                  <c:v>0.1060000000000004</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>4.760000000000017E-2</c:v>
+                  <c:v>2.7200000000000099E-2</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>1.5999999999999771E-2</c:v>
+                  <c:v>2.3999999999999654E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2.5600000000000091E-2</c:v>
+                  <c:v>4.0800000000000149E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>2.5600000000000091E-2</c:v>
+                  <c:v>2.6400000000000094E-2</c:v>
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0</c:v>
@@ -8824,262 +8824,262 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.11000000000000136</c:v>
+                  <c:v>0.11080000000000216</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29759999999999981</c:v>
+                  <c:v>0.29639999999999639</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.31319999999999987</c:v>
+                  <c:v>0.31519999999999965</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.32680000000000015</c:v>
+                  <c:v>0.32920000000000255</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.33159999999999606</c:v>
+                  <c:v>0.3424000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35160000000000347</c:v>
+                  <c:v>0.3519999999999972</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.36680000000000013</c:v>
+                  <c:v>0.36520000000000297</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.37679999999999986</c:v>
+                  <c:v>0.37399999999999928</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.38559999999999894</c:v>
+                  <c:v>0.39279999999999726</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.40719999999999829</c:v>
+                  <c:v>0.40399999999999958</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.41600000000000265</c:v>
+                  <c:v>0.41400000000000287</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.44200000000000172</c:v>
+                  <c:v>0.43720000000000137</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.46359999999999918</c:v>
+                  <c:v>0.4624000000000002</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.47279999999999722</c:v>
+                  <c:v>0.47999999999999554</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.50920000000000032</c:v>
+                  <c:v>0.48520000000000296</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.5004000000000004</c:v>
+                  <c:v>0.5095999999999985</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.52920000000000045</c:v>
+                  <c:v>0.52680000000000249</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.5327999999999995</c:v>
+                  <c:v>0.54079999999999862</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.56519999999999848</c:v>
+                  <c:v>0.54759999999999875</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.55519999999999969</c:v>
+                  <c:v>0.56040000000000267</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.57920000000000138</c:v>
+                  <c:v>0.58439999999999548</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.5916000000000009</c:v>
+                  <c:v>0.60160000000000424</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.63159999999999827</c:v>
+                  <c:v>0.63600000000000045</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.61600000000000266</c:v>
+                  <c:v>0.6071999999999983</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.64999999999999891</c:v>
+                  <c:v>0.64360000000000139</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.66119999999999679</c:v>
+                  <c:v>0.67279999999999729</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.67920000000000225</c:v>
+                  <c:v>0.66400000000000026</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.68320000000000014</c:v>
+                  <c:v>0.68239999999999934</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0.69600000000000128</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0.71560000000000101</c:v>
                 </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.70640000000000291</c:v>
-                </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.69759999999999678</c:v>
+                  <c:v>0.71759999999999891</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.70119999999999982</c:v>
+                  <c:v>0.76600000000000279</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.75439999999999552</c:v>
+                  <c:v>0.72599999999999609</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.75160000000000604</c:v>
+                  <c:v>0.70880000000000087</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.76440000000000108</c:v>
+                  <c:v>0.81480000000000286</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.77399999999999503</c:v>
+                  <c:v>0.76039999999999486</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.79320000000000335</c:v>
+                  <c:v>0.79800000000000382</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.78799999999999559</c:v>
+                  <c:v>0.79399999999999715</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.79880000000000462</c:v>
+                  <c:v>0.78520000000000201</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.74600000000000266</c:v>
+                  <c:v>0.72240000000000337</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.72319999999999551</c:v>
+                  <c:v>0.8187999999999952</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.77640000000000209</c:v>
+                  <c:v>0.67040000000000222</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.77719999999999601</c:v>
+                  <c:v>0.72439999999999671</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.74520000000000186</c:v>
+                  <c:v>0.74840000000000284</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.74040000000000372</c:v>
+                  <c:v>0.73840000000000172</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.65119999999999723</c:v>
+                  <c:v>0.73319999999999663</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.73640000000000194</c:v>
+                  <c:v>0.75680000000000236</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.61799999999999744</c:v>
+                  <c:v>0.72679999999999689</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.62920000000000087</c:v>
+                  <c:v>0.602800000000001</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.70240000000000324</c:v>
+                  <c:v>0.63680000000000181</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.63439999999999608</c:v>
+                  <c:v>0.60519999999999807</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.62280000000000779</c:v>
+                  <c:v>0.69120000000000814</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.57559999999999745</c:v>
+                  <c:v>0.56719999999999693</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.57200000000000117</c:v>
+                  <c:v>0.54320000000000224</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.48279999999999845</c:v>
+                  <c:v>0.53439999999999643</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.61200000000000143</c:v>
+                  <c:v>0.52320000000000222</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.50120000000000231</c:v>
+                  <c:v>0.41800000000000098</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.46039999999999726</c:v>
+                  <c:v>0.48119999999999796</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.34680000000000166</c:v>
+                  <c:v>0.41240000000000199</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.38519999999999793</c:v>
+                  <c:v>0.34879999999999728</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.39200000000000096</c:v>
+                  <c:v>0.2852000000000009</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.256000000000001</c:v>
+                  <c:v>0.37560000000000171</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.43279999999999752</c:v>
+                  <c:v>0.3319999999999983</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.32000000000000139</c:v>
+                  <c:v>0.26880000000000109</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.23319999999999827</c:v>
+                  <c:v>0.30519999999999831</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.30680000000000152</c:v>
+                  <c:v>0.30400000000000088</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.27480000000000104</c:v>
+                  <c:v>0.26840000000000125</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.35200000000000137</c:v>
+                  <c:v>0.33160000000000084</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.35319999999999463</c:v>
+                  <c:v>0.29199999999999587</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.37160000000000132</c:v>
+                  <c:v>0.34280000000000127</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.22760000000000083</c:v>
+                  <c:v>0.33360000000000117</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.2484000000000009</c:v>
+                  <c:v>0.3020000000000011</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.31560000000000116</c:v>
+                  <c:v>0.26040000000000102</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.1835999999999974</c:v>
+                  <c:v>0.2311999999999966</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.2048000000000007</c:v>
+                  <c:v>0.15360000000000068</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.28520000000000106</c:v>
+                  <c:v>0.21680000000000069</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.16960000000000064</c:v>
+                  <c:v>0.23000000000000087</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.12920000000000048</c:v>
+                  <c:v>0.15840000000000057</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.10599999999999847</c:v>
+                  <c:v>9.6799999999998596E-2</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>4.040000000000013E-2</c:v>
+                  <c:v>0.1124000000000004</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>7.200000000000044E-3</c:v>
+                  <c:v>1.0800000000000014E-2</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>3.9999999999999897E-3</c:v>
+                  <c:v>9.5600000000000365E-2</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.11080000000000041</c:v>
+                  <c:v>1.1999999999999988E-3</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>7.9999999999999071E-4</c:v>
+                  <c:v>3.1599999999999559E-2</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>6.8000000000000204E-3</c:v>
+                  <c:v>3.5600000000000125E-2</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>3.8000000000000138E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="88">
                   <c:v>0</c:v>
@@ -9427,226 +9427,226 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.12719999999999859</c:v>
+                  <c:v>0.12919999999999837</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35800000000000021</c:v>
+                  <c:v>0.36280000000000057</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.38720000000000054</c:v>
+                  <c:v>0.39480000000000148</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4003999999999982</c:v>
+                  <c:v>0.39679999999999682</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.38839999999999952</c:v>
+                  <c:v>0.38880000000000214</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.36480000000000118</c:v>
+                  <c:v>0.36159999999999798</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.34680000000000233</c:v>
+                  <c:v>0.35040000000000371</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.32999999999999963</c:v>
+                  <c:v>0.32759999999999723</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.31600000000000045</c:v>
+                  <c:v>0.31439999999999885</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.30319999999999653</c:v>
+                  <c:v>0.30840000000000395</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.29680000000000345</c:v>
+                  <c:v>0.29639999999999639</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.29119999999999918</c:v>
+                  <c:v>0.28880000000000117</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.28599999999999931</c:v>
+                  <c:v>0.28080000000000083</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.27919999999999923</c:v>
+                  <c:v>0.28360000000000135</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.27600000000000047</c:v>
+                  <c:v>0.28199999999999975</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.27680000000000127</c:v>
+                  <c:v>0.28359999999999691</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.27800000000000147</c:v>
+                  <c:v>0.27000000000000229</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.28000000000000003</c:v>
+                  <c:v>0.27359999999999807</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.28199999999999975</c:v>
+                  <c:v>0.28119999999999901</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.28399999999999953</c:v>
+                  <c:v>0.28040000000000265</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.28039999999999821</c:v>
+                  <c:v>0.28799999999999909</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.30199999999999888</c:v>
+                  <c:v>0.3040000000000031</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.31880000000000103</c:v>
+                  <c:v>0.31559999999999783</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.32719999999999833</c:v>
+                  <c:v>0.33119999999999788</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.35200000000000087</c:v>
+                  <c:v>0.35080000000000189</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.36560000000000115</c:v>
+                  <c:v>0.37160000000000049</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.38920000000000204</c:v>
+                  <c:v>0.40600000000000114</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.4271999999999942</c:v>
+                  <c:v>0.41799999999999615</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.44360000000000332</c:v>
+                  <c:v>0.43720000000000137</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4608000000000006</c:v>
+                  <c:v>0.45200000000000068</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.49120000000000014</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.52400000000000191</c:v>
+                  <c:v>0.50960000000000072</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.57679999999999643</c:v>
+                  <c:v>0.59159999999999568</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.63280000000000003</c:v>
+                  <c:v>0.6408000000000037</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.70400000000000496</c:v>
+                  <c:v>0.66280000000000128</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.72759999999999325</c:v>
+                  <c:v>0.75439999999999552</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.80640000000000556</c:v>
+                  <c:v>0.81960000000000321</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.82799999999999319</c:v>
+                  <c:v>0.84079999999999711</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.92880000000000407</c:v>
+                  <c:v>0.90680000000000194</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.0044000000000022</c:v>
+                  <c:v>1.0200000000000022</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.0227999999999982</c:v>
+                  <c:v>1.062799999999998</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.1740000000000037</c:v>
+                  <c:v>1.1060000000000021</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.2007999999999932</c:v>
+                  <c:v>1.1555999999999949</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.2516000000000038</c:v>
+                  <c:v>1.279600000000003</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.2348000000000048</c:v>
+                  <c:v>1.3028000000000064</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.3287999999999918</c:v>
+                  <c:v>1.2723999999999911</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.2144000000000041</c:v>
+                  <c:v>1.1920000000000062</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.2783999999999949</c:v>
+                  <c:v>1.3283999999999914</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.2652000000000041</c:v>
+                  <c:v>1.2404000000000059</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.1372000000000022</c:v>
+                  <c:v>1.0788000000000035</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.1811999999999949</c:v>
+                  <c:v>1.1839999999999933</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.0724000000000133</c:v>
+                  <c:v>1.2252000000000149</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.0799999999999941</c:v>
+                  <c:v>1.0791999999999944</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.0944000000000038</c:v>
+                  <c:v>0.92720000000000358</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.85079999999999589</c:v>
+                  <c:v>0.81079999999999497</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.65600000000000225</c:v>
+                  <c:v>0.84080000000000343</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.7700000000000029</c:v>
+                  <c:v>0.6948000000000023</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.55959999999999654</c:v>
+                  <c:v>0.60239999999999694</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.56200000000000228</c:v>
+                  <c:v>0.50960000000000183</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4971999999999972</c:v>
+                  <c:v>0.62199999999999678</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.39560000000000151</c:v>
+                  <c:v>0.35920000000000135</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.33080000000000115</c:v>
+                  <c:v>0.23320000000000063</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.25799999999999851</c:v>
+                  <c:v>0.34919999999999818</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.33920000000000128</c:v>
+                  <c:v>0.15640000000000071</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.19039999999999899</c:v>
+                  <c:v>0.28879999999999834</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.18040000000000064</c:v>
+                  <c:v>0.15240000000000059</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.24120000000000089</c:v>
+                  <c:v>0.21200000000000072</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.19520000000000065</c:v>
+                  <c:v>0.15960000000000052</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.17239999999999756</c:v>
+                  <c:v>0.22519999999999682</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>6.4800000000000232E-2</c:v>
+                  <c:v>0.15880000000000055</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>4.6800000000000168E-2</c:v>
+                  <c:v>2.3600000000000093E-2</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>5.2400000000000183E-2</c:v>
+                  <c:v>7.2800000000000253E-2</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>2.1200000000000069E-2</c:v>
+                  <c:v>1.8000000000000065E-2</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>3.7199999999999477E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -10030,217 +10030,217 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.6799999999999234E-2</c:v>
+                  <c:v>9.4400000000001275E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.24640000000000195</c:v>
+                  <c:v>0.25119999999999787</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.25840000000000063</c:v>
+                  <c:v>0.25920000000000143</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.25239999999999685</c:v>
+                  <c:v>0.26199999999999757</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.25240000000000129</c:v>
+                  <c:v>0.26159999999999939</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.25280000000000002</c:v>
+                  <c:v>0.25360000000000082</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.25119999999999787</c:v>
+                  <c:v>0.25360000000000027</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.26120000000000176</c:v>
+                  <c:v>0.25520000000000242</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.25720000000000165</c:v>
+                  <c:v>0.25879999999999881</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.25399999999999845</c:v>
+                  <c:v>0.25279999999999947</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.25840000000000063</c:v>
+                  <c:v>0.26040000000000041</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.26319999999999771</c:v>
+                  <c:v>0.26279999999999953</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.25959999999999961</c:v>
+                  <c:v>0.26480000000000259</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.26240000000000019</c:v>
+                  <c:v>0.26479999999999815</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.26839999999999953</c:v>
+                  <c:v>0.26599999999999713</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.27800000000000025</c:v>
+                  <c:v>0.27160000000000273</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.27000000000000229</c:v>
+                  <c:v>0.27759999999999885</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.28239999999999793</c:v>
+                  <c:v>0.28320000000000317</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.28480000000000033</c:v>
+                  <c:v>0.29839999999999617</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.30760000000000315</c:v>
+                  <c:v>0.31560000000000227</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.32839999999999731</c:v>
+                  <c:v>0.32639999999999753</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.33680000000000054</c:v>
+                  <c:v>0.34360000000000068</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.37360000000000027</c:v>
+                  <c:v>0.36560000000000115</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.39239999999999908</c:v>
+                  <c:v>0.38559999999999894</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.42320000000000096</c:v>
+                  <c:v>0.4283999999999995</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.44760000000000094</c:v>
+                  <c:v>0.44440000000000218</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.47959999999999953</c:v>
+                  <c:v>0.50440000000000218</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.51879999999999871</c:v>
+                  <c:v>0.52199999999999747</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.56159999999999966</c:v>
+                  <c:v>0.56359999999999943</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.6032000000000014</c:v>
+                  <c:v>0.61280000000000223</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.65839999999999765</c:v>
+                  <c:v>0.67119999999999713</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0.71520000000000283</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.77399999999999503</c:v>
+                  <c:v>0.78359999999999563</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.84000000000000374</c:v>
+                  <c:v>0.88520000000000243</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.93960000000000377</c:v>
+                  <c:v>0.96880000000000421</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.0267999999999933</c:v>
+                  <c:v>1.0367999999999922</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.2316000000000038</c:v>
+                  <c:v>1.1580000000000055</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.2559999999999971</c:v>
+                  <c:v>1.2339999999999951</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.3120000000000023</c:v>
+                  <c:v>1.3236000000000028</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.4252000000000071</c:v>
+                  <c:v>1.3476000000000048</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.3271999999999924</c:v>
+                  <c:v>1.3223999999999942</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.4144000000000052</c:v>
+                  <c:v>1.433200000000004</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.2983999999999927</c:v>
+                  <c:v>1.3827999999999923</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.366800000000004</c:v>
+                  <c:v>1.3416000000000052</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.2412000000000045</c:v>
+                  <c:v>1.2492000000000036</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.2063999999999944</c:v>
+                  <c:v>1.163599999999994</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.2160000000000035</c:v>
+                  <c:v>1.1988000000000041</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.1327999999999945</c:v>
+                  <c:v>1.116799999999994</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.2128000000000037</c:v>
+                  <c:v>1.0980000000000052</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.0708000000000044</c:v>
+                  <c:v>0.9688000000000031</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.99039999999999373</c:v>
+                  <c:v>1.0779999999999943</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.85200000000001108</c:v>
+                  <c:v>0.95680000000001175</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.73079999999999645</c:v>
+                  <c:v>0.69079999999999664</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.7292000000000024</c:v>
+                  <c:v>0.65240000000000198</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.75119999999999565</c:v>
+                  <c:v>0.6631999999999969</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.68080000000000274</c:v>
+                  <c:v>0.67320000000000235</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.37200000000000144</c:v>
+                  <c:v>0.50600000000000156</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.37839999999999785</c:v>
+                  <c:v>0.3859999999999979</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.31280000000000113</c:v>
+                  <c:v>0.35960000000000147</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.19039999999999899</c:v>
+                  <c:v>0.23399999999999879</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.33320000000000105</c:v>
+                  <c:v>0.22160000000000063</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.20560000000000067</c:v>
+                  <c:v>0.20800000000000088</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.21519999999999898</c:v>
+                  <c:v>0.21959999999999877</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.22360000000000071</c:v>
+                  <c:v>0.27560000000000101</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.31639999999999835</c:v>
+                  <c:v>0.20799999999999888</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.1484000000000005</c:v>
+                  <c:v>0.25400000000000089</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.1556000000000006</c:v>
+                  <c:v>0.14040000000000047</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>7.7200000000000255E-2</c:v>
+                  <c:v>0.12640000000000046</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>6.6799999999999055E-2</c:v>
+                  <c:v>4.1999999999999392E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>2.1600000000000077E-2</c:v>
+                  <c:v>2.0000000000000078E-3</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0</c:v>
+                  <c:v>3.880000000000014E-2</c:v>
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>0</c:v>
@@ -17852,11 +17852,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="H5">
-        <v>0.99443999999999999</v>
+        <v>0.99467000000000005</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5:I68" si="4">(H4-H5)/(G5-G4)</f>
-        <v>0.22240000000000068</v>
+        <v>0.21319999999999811</v>
       </c>
       <c r="K5">
         <v>0.5</v>
@@ -17896,11 +17896,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="H6">
-        <v>0.97831999999999997</v>
+        <v>0.97904999999999998</v>
       </c>
       <c r="I6">
         <f t="shared" si="4"/>
-        <v>0.64480000000000037</v>
+        <v>0.62480000000000258</v>
       </c>
       <c r="K6">
         <v>0.75</v>
@@ -17940,11 +17940,11 @@
         <v>0.39</v>
       </c>
       <c r="H7">
-        <v>0.95975999999999995</v>
+        <v>0.96155000000000002</v>
       </c>
       <c r="I7">
         <f t="shared" si="4"/>
-        <v>0.74240000000000017</v>
+        <v>0.69999999999999774</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -17984,11 +17984,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="H8">
-        <v>0.93945999999999996</v>
+        <v>0.94221999999999995</v>
       </c>
       <c r="I8">
         <f t="shared" si="4"/>
-        <v>0.81199999999999872</v>
+        <v>0.77320000000000211</v>
       </c>
       <c r="K8">
         <v>1.25</v>
@@ -18028,11 +18028,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="H9">
-        <v>0.91935</v>
+        <v>0.92252000000000001</v>
       </c>
       <c r="I9">
         <f t="shared" si="4"/>
-        <v>0.80439999999999778</v>
+        <v>0.78799999999999693</v>
       </c>
       <c r="K9">
         <v>1.5</v>
@@ -18072,11 +18072,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="H10">
-        <v>0.89834999999999998</v>
+        <v>0.90273999999999999</v>
       </c>
       <c r="I10">
         <f t="shared" si="4"/>
-        <v>0.84000000000000186</v>
+        <v>0.79120000000000179</v>
       </c>
       <c r="K10">
         <v>1.75</v>
@@ -18116,11 +18116,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="H11">
-        <v>0.87931999999999999</v>
+        <v>0.88307000000000002</v>
       </c>
       <c r="I11">
         <f t="shared" si="4"/>
-        <v>0.76119999999999899</v>
+        <v>0.78679999999999795</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -18160,11 +18160,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="H12">
-        <v>0.85911999999999999</v>
+        <v>0.86360000000000003</v>
       </c>
       <c r="I12">
         <f t="shared" si="4"/>
-        <v>0.80800000000000094</v>
+        <v>0.77880000000000049</v>
       </c>
       <c r="K12">
         <v>2.25</v>
@@ -18204,11 +18204,11 @@
         <v>0.54</v>
       </c>
       <c r="H13">
-        <v>0.83880999999999994</v>
+        <v>0.84367000000000003</v>
       </c>
       <c r="I13">
         <f t="shared" si="4"/>
-        <v>0.81240000000000134</v>
+        <v>0.79719999999999946</v>
       </c>
       <c r="K13">
         <v>2.5</v>
@@ -18248,11 +18248,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="H14">
-        <v>0.81954000000000005</v>
+        <v>0.82355999999999996</v>
       </c>
       <c r="I14">
         <f t="shared" si="4"/>
-        <v>0.77079999999999527</v>
+        <v>0.80440000000000222</v>
       </c>
       <c r="K14">
         <v>2.75</v>
@@ -18292,11 +18292,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="H15">
-        <v>0.79944999999999999</v>
+        <v>0.80308000000000002</v>
       </c>
       <c r="I15">
         <f t="shared" si="4"/>
-        <v>0.80360000000000142</v>
+        <v>0.81919999999999693</v>
       </c>
       <c r="K15">
         <v>3</v>
@@ -18336,11 +18336,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="H16">
-        <v>0.77888999999999997</v>
+        <v>0.7833</v>
       </c>
       <c r="I16">
         <f t="shared" si="4"/>
-        <v>0.82240000000000379</v>
+        <v>0.79120000000000357</v>
       </c>
       <c r="K16">
         <v>3.25</v>
@@ -18380,11 +18380,11 @@
         <v>0.64</v>
       </c>
       <c r="H17">
-        <v>0.75960000000000005</v>
+        <v>0.76310999999999996</v>
       </c>
       <c r="I17">
         <f t="shared" si="4"/>
-        <v>0.77159999999999607</v>
+        <v>0.80760000000000098</v>
       </c>
       <c r="K17">
         <v>3.5</v>
@@ -18424,11 +18424,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="H18">
-        <v>0.74136000000000002</v>
+        <v>0.74426999999999999</v>
       </c>
       <c r="I18">
         <f t="shared" si="4"/>
-        <v>0.72960000000000069</v>
+        <v>0.75359999999999805</v>
       </c>
       <c r="K18">
         <v>3.75</v>
@@ -18468,11 +18468,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="H19">
-        <v>0.72209000000000001</v>
+        <v>0.72497999999999996</v>
       </c>
       <c r="I19">
         <f t="shared" si="4"/>
-        <v>0.77079999999999971</v>
+        <v>0.77160000000000051</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -18512,11 +18512,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="H20">
-        <v>0.70352999999999999</v>
+        <v>0.70520000000000005</v>
       </c>
       <c r="I20">
         <f t="shared" si="4"/>
-        <v>0.74240000000000017</v>
+        <v>0.79119999999999568</v>
       </c>
       <c r="K20">
         <v>4.25</v>
@@ -18556,11 +18556,11 @@
         <v>0.74</v>
       </c>
       <c r="H21">
-        <v>0.68252999999999997</v>
+        <v>0.6835</v>
       </c>
       <c r="I21">
         <f t="shared" si="4"/>
-        <v>0.84000000000000374</v>
+        <v>0.86800000000000521</v>
       </c>
       <c r="K21">
         <v>4.5</v>
@@ -18600,11 +18600,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="H22">
-        <v>0.66364999999999996</v>
+        <v>0.66295000000000004</v>
       </c>
       <c r="I22">
         <f t="shared" si="4"/>
-        <v>0.75519999999999965</v>
+        <v>0.82199999999999751</v>
       </c>
       <c r="K22">
         <v>4.75</v>
@@ -18644,11 +18644,11 @@
         <v>0.79</v>
       </c>
       <c r="H23">
-        <v>0.64181999999999995</v>
+        <v>0.64168000000000003</v>
       </c>
       <c r="I23">
         <f t="shared" si="4"/>
-        <v>0.87319999999999987</v>
+        <v>0.85079999999999967</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -18688,11 +18688,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="H24">
-        <v>0.62170999999999998</v>
+        <v>0.62080000000000002</v>
       </c>
       <c r="I24">
         <f t="shared" si="4"/>
-        <v>0.80439999999999778</v>
+        <v>0.83519999999999961</v>
       </c>
       <c r="K24">
         <v>5.25</v>
@@ -18732,11 +18732,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="H25">
-        <v>0.60060000000000002</v>
+        <v>0.59989999999999999</v>
       </c>
       <c r="I25">
         <f t="shared" si="4"/>
-        <v>0.84439999999999771</v>
+        <v>0.83600000000000041</v>
       </c>
       <c r="K25">
         <v>5.5</v>
@@ -18776,11 +18776,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="H26">
-        <v>0.57850999999999997</v>
+        <v>0.57884999999999998</v>
       </c>
       <c r="I26">
         <f t="shared" si="4"/>
-        <v>0.88360000000000527</v>
+        <v>0.84200000000000352</v>
       </c>
       <c r="K26">
         <v>5.75</v>
@@ -18820,11 +18820,11 @@
         <v>0.89</v>
       </c>
       <c r="H27">
-        <v>0.55657000000000001</v>
+        <v>0.55964999999999998</v>
       </c>
       <c r="I27">
         <f t="shared" si="4"/>
-        <v>0.8775999999999976</v>
+        <v>0.76799999999999913</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -18864,11 +18864,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="H28">
-        <v>0.53517999999999999</v>
+        <v>0.53959000000000001</v>
       </c>
       <c r="I28">
         <f t="shared" si="4"/>
-        <v>0.85560000000000003</v>
+        <v>0.802399999999998</v>
       </c>
       <c r="K28">
         <v>6.25</v>
@@ -18908,11 +18908,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="H29">
-        <v>0.51492000000000004</v>
+        <v>0.51987000000000005</v>
       </c>
       <c r="I29">
         <f t="shared" si="4"/>
-        <v>0.81039999999999712</v>
+        <v>0.78879999999999773</v>
       </c>
       <c r="K29">
         <v>6.5</v>
@@ -18952,11 +18952,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="H30">
-        <v>0.49386000000000002</v>
+        <v>0.49715999999999999</v>
       </c>
       <c r="I30">
         <f t="shared" si="4"/>
-        <v>0.84240000000000015</v>
+        <v>0.90840000000000176</v>
       </c>
       <c r="K30">
         <v>6.75</v>
@@ -18996,11 +18996,11 @@
         <v>0.99</v>
       </c>
       <c r="H31">
-        <v>0.47422999999999998</v>
+        <v>0.47576000000000002</v>
       </c>
       <c r="I31">
         <f t="shared" si="4"/>
-        <v>0.78520000000000423</v>
+        <v>0.85600000000000198</v>
       </c>
       <c r="K31">
         <v>7</v>
@@ -19040,11 +19040,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="H32">
-        <v>0.4491</v>
+        <v>0.45086999999999999</v>
       </c>
       <c r="I32">
         <f t="shared" si="4"/>
-        <v>1.0051999999999941</v>
+        <v>0.9955999999999956</v>
       </c>
       <c r="K32">
         <v>7.25</v>
@@ -19084,11 +19084,11 @@
         <v>1.04</v>
       </c>
       <c r="H33">
-        <v>0.42802000000000001</v>
+        <v>0.42863000000000001</v>
       </c>
       <c r="I33">
         <f t="shared" si="4"/>
-        <v>0.8432000000000025</v>
+        <v>0.88960000000000239</v>
       </c>
       <c r="K33">
         <v>7.5</v>
@@ -19128,11 +19128,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="H34">
-        <v>0.40673999999999999</v>
+        <v>0.40649999999999997</v>
       </c>
       <c r="I34">
         <f t="shared" si="4"/>
-        <v>0.85120000000000384</v>
+        <v>0.88520000000000465</v>
       </c>
       <c r="K34">
         <v>7.75</v>
@@ -19172,11 +19172,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="H35">
-        <v>0.38606000000000001</v>
+        <v>0.38744000000000001</v>
       </c>
       <c r="I35">
         <f t="shared" si="4"/>
-        <v>0.82719999999999461</v>
+        <v>0.76239999999999453</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -19216,11 +19216,11 @@
         <v>1.115</v>
       </c>
       <c r="H36">
-        <v>0.36723</v>
+        <v>0.36614999999999998</v>
       </c>
       <c r="I36">
         <f t="shared" si="4"/>
-        <v>0.7532000000000032</v>
+        <v>0.85160000000000424</v>
       </c>
       <c r="K36">
         <v>8.25</v>
@@ -19260,11 +19260,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="H37">
-        <v>0.34813</v>
+        <v>0.34895999999999999</v>
       </c>
       <c r="I37">
         <f t="shared" si="4"/>
-        <v>0.76399999999999613</v>
+        <v>0.68759999999999566</v>
       </c>
       <c r="K37">
         <v>8.5</v>
@@ -19304,11 +19304,11 @@
         <v>1.165</v>
       </c>
       <c r="H38">
-        <v>0.33091999999999999</v>
+        <v>0.33184999999999998</v>
       </c>
       <c r="I38">
         <f t="shared" si="4"/>
-        <v>0.68840000000000257</v>
+        <v>0.68440000000000301</v>
       </c>
       <c r="K38">
         <v>8.75</v>
@@ -19348,11 +19348,11 @@
         <v>1.19</v>
       </c>
       <c r="H39">
-        <v>0.31158000000000002</v>
+        <v>0.31640000000000001</v>
       </c>
       <c r="I39">
         <f t="shared" si="4"/>
-        <v>0.77360000000000151</v>
+        <v>0.61800000000000077</v>
       </c>
       <c r="K39">
         <v>9</v>
@@ -19392,11 +19392,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="H40">
-        <v>0.29382999999999998</v>
+        <v>0.29966999999999999</v>
       </c>
       <c r="I40">
         <f t="shared" si="4"/>
-        <v>0.70999999999999797</v>
+        <v>0.66919999999999735</v>
       </c>
       <c r="K40">
         <v>9.25</v>
@@ -19436,11 +19436,11 @@
         <v>1.24</v>
       </c>
       <c r="H41">
-        <v>0.27465000000000001</v>
+        <v>0.28175</v>
       </c>
       <c r="I41">
         <f t="shared" si="4"/>
-        <v>0.76720000000000177</v>
+        <v>0.71680000000000221</v>
       </c>
       <c r="K41">
         <v>9.5</v>
@@ -19480,11 +19480,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="H42">
-        <v>0.26384999999999997</v>
+        <v>0.26543</v>
       </c>
       <c r="I42">
         <f t="shared" si="4"/>
-        <v>0.431999999999999</v>
+        <v>0.65279999999999661</v>
       </c>
       <c r="K42">
         <v>9.75</v>
@@ -19524,11 +19524,11 @@
         <v>1.29</v>
       </c>
       <c r="H43">
-        <v>0.24858</v>
+        <v>0.24928</v>
       </c>
       <c r="I43">
         <f t="shared" si="4"/>
-        <v>0.61080000000000134</v>
+        <v>0.64600000000000224</v>
       </c>
       <c r="K43">
         <v>10</v>
@@ -19568,11 +19568,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="H44">
-        <v>0.23394000000000001</v>
+        <v>0.23405999999999999</v>
       </c>
       <c r="I44">
         <f t="shared" si="4"/>
-        <v>0.58560000000000156</v>
+        <v>0.60880000000000256</v>
       </c>
       <c r="K44">
         <v>10.25</v>
@@ -19612,11 +19612,11 @@
         <v>1.34</v>
       </c>
       <c r="H45">
-        <v>0.21839</v>
+        <v>0.21931</v>
       </c>
       <c r="I45">
         <f t="shared" si="4"/>
-        <v>0.621999999999997</v>
+        <v>0.58999999999999631</v>
       </c>
       <c r="K45">
         <v>10.5</v>
@@ -19656,11 +19656,11 @@
         <v>1.365</v>
       </c>
       <c r="H46">
-        <v>0.19545999999999999</v>
+        <v>0.20033999999999999</v>
       </c>
       <c r="I46">
         <f t="shared" si="4"/>
-        <v>0.91720000000000346</v>
+        <v>0.75880000000000325</v>
       </c>
       <c r="K46">
         <v>10.75</v>
@@ -19700,11 +19700,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="H47">
-        <v>0.17996999999999999</v>
+        <v>0.18392</v>
       </c>
       <c r="I47">
         <f t="shared" si="4"/>
-        <v>0.61959999999999682</v>
+        <v>0.65679999999999605</v>
       </c>
       <c r="K47">
         <v>11</v>
@@ -19744,11 +19744,11 @@
         <v>1.415</v>
       </c>
       <c r="H48">
-        <v>0.16769999999999999</v>
+        <v>0.17041000000000001</v>
       </c>
       <c r="I48">
         <f t="shared" si="4"/>
-        <v>0.49080000000000185</v>
+        <v>0.54040000000000166</v>
       </c>
       <c r="K48">
         <v>11.25</v>
@@ -19788,11 +19788,11 @@
         <v>1.44</v>
       </c>
       <c r="H49">
-        <v>0.15140000000000001</v>
+        <v>0.15675</v>
       </c>
       <c r="I49">
         <f t="shared" si="4"/>
-        <v>0.65200000000000158</v>
+        <v>0.54640000000000211</v>
       </c>
       <c r="K49">
         <v>11.5</v>
@@ -19832,11 +19832,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="H50">
-        <v>0.14030000000000001</v>
+        <v>0.14373</v>
       </c>
       <c r="I50">
         <f t="shared" si="4"/>
-        <v>0.44399999999999756</v>
+        <v>0.52079999999999738</v>
       </c>
       <c r="K50">
         <v>11.75</v>
@@ -19876,11 +19876,11 @@
         <v>1.49</v>
       </c>
       <c r="H51">
-        <v>0.13197999999999999</v>
+        <v>0.13199</v>
       </c>
       <c r="I51">
         <f t="shared" si="4"/>
-        <v>0.33280000000000204</v>
+        <v>0.46960000000000168</v>
       </c>
       <c r="K51">
         <v>12</v>
@@ -19920,11 +19920,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="H52">
-        <v>0.11756</v>
+        <v>0.1182</v>
       </c>
       <c r="I52">
         <f t="shared" si="4"/>
-        <v>0.57679999999999643</v>
+        <v>0.55159999999999698</v>
       </c>
       <c r="K52">
         <v>12.25</v>
@@ -19964,11 +19964,11 @@
         <v>1.54</v>
       </c>
       <c r="H53">
-        <v>0.10623</v>
+        <v>9.9909999999999999E-2</v>
       </c>
       <c r="I53">
         <f t="shared" si="4"/>
-        <v>0.45320000000000132</v>
+        <v>0.73160000000000258</v>
       </c>
       <c r="K53">
         <v>12.5</v>
@@ -20008,11 +20008,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="H54">
-        <v>9.035E-2</v>
+        <v>8.7720000000000006E-2</v>
       </c>
       <c r="I54">
         <f t="shared" si="4"/>
-        <v>0.63520000000000243</v>
+        <v>0.48760000000000142</v>
       </c>
       <c r="K54">
         <v>12.75</v>
@@ -20052,11 +20052,11 @@
         <v>1.59</v>
       </c>
       <c r="H55">
-        <v>8.7150000000000005E-2</v>
+        <v>8.3030000000000007E-2</v>
       </c>
       <c r="I55">
         <f t="shared" si="4"/>
-        <v>0.12799999999999909</v>
+        <v>0.18759999999999899</v>
       </c>
       <c r="K55">
         <v>13</v>
@@ -20096,11 +20096,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="H56">
-        <v>7.8689999999999996E-2</v>
+        <v>7.7789999999999998E-2</v>
       </c>
       <c r="I56">
         <f t="shared" si="4"/>
-        <v>0.33840000000000459</v>
+        <v>0.20960000000000295</v>
       </c>
       <c r="K56">
         <v>13.25</v>
@@ -20140,11 +20140,11 @@
         <v>1.64</v>
       </c>
       <c r="H57">
-        <v>7.3969999999999994E-2</v>
+        <v>7.2459999999999997E-2</v>
       </c>
       <c r="I57">
         <f t="shared" si="4"/>
-        <v>0.18879999999999908</v>
+        <v>0.21319999999999892</v>
       </c>
       <c r="K57">
         <v>13.5</v>
@@ -20184,11 +20184,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="H58">
-        <v>6.6430000000000003E-2</v>
+        <v>6.6220000000000001E-2</v>
       </c>
       <c r="I58">
         <f t="shared" si="4"/>
-        <v>0.3016000000000007</v>
+        <v>0.24960000000000071</v>
       </c>
       <c r="K58">
         <v>13.75</v>
@@ -20228,11 +20228,11 @@
         <v>1.69</v>
       </c>
       <c r="H59">
-        <v>6.2100000000000002E-2</v>
+        <v>5.8689999999999999E-2</v>
       </c>
       <c r="I59">
         <f t="shared" si="4"/>
-        <v>0.1731999999999991</v>
+        <v>0.30119999999999847</v>
       </c>
       <c r="K59">
         <v>14</v>
@@ -20272,11 +20272,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="H60">
-        <v>5.4760000000000003E-2</v>
+        <v>5.1229999999999998E-2</v>
       </c>
       <c r="I60">
         <f t="shared" si="4"/>
-        <v>0.29360000000000103</v>
+        <v>0.29840000000000111</v>
       </c>
       <c r="K60">
         <v>14.25</v>
@@ -20316,11 +20316,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="H61">
-        <v>3.7269999999999998E-2</v>
+        <v>4.1029999999999997E-2</v>
       </c>
       <c r="I61">
         <f t="shared" si="4"/>
-        <v>0.69960000000000266</v>
+        <v>0.40800000000000147</v>
       </c>
       <c r="K61">
         <v>14.5</v>
@@ -20360,11 +20360,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="H62">
-        <v>2.8649999999999998E-2</v>
+        <v>3.4790000000000001E-2</v>
       </c>
       <c r="I62">
         <f t="shared" si="4"/>
-        <v>0.34479999999999811</v>
+        <v>0.24959999999999849</v>
       </c>
       <c r="K62">
         <v>14.75</v>
@@ -20404,11 +20404,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="H63">
-        <v>2.7119999999999998E-2</v>
+        <v>2.7650000000000001E-2</v>
       </c>
       <c r="I63">
         <f t="shared" si="4"/>
-        <v>6.120000000000022E-2</v>
+        <v>0.28560000000000102</v>
       </c>
       <c r="K63">
         <v>15</v>
@@ -20448,11 +20448,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="H64">
-        <v>2.6200000000000001E-2</v>
+        <v>2.6519999999999998E-2</v>
       </c>
       <c r="I64">
         <f t="shared" si="4"/>
-        <v>3.6799999999999694E-2</v>
+        <v>4.5199999999999858E-2</v>
       </c>
       <c r="K64">
         <v>15.25</v>
@@ -20492,11 +20492,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="H65">
-        <v>2.529E-2</v>
+        <v>2.545E-2</v>
       </c>
       <c r="I65">
         <f t="shared" si="4"/>
-        <v>3.6400000000000175E-2</v>
+        <v>4.2800000000000074E-2</v>
       </c>
       <c r="K65">
         <v>15.5</v>
@@ -20536,11 +20536,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="H66">
-        <v>2.5059999999999999E-2</v>
+        <v>2.4709999999999999E-2</v>
       </c>
       <c r="I66">
         <f t="shared" si="4"/>
-        <v>9.2000000000000744E-3</v>
+        <v>2.9600000000000147E-2</v>
       </c>
       <c r="K66">
         <v>15.75</v>
@@ -20580,11 +20580,11 @@
         <v>1.89</v>
       </c>
       <c r="H67">
-        <v>2.3910000000000001E-2</v>
+        <v>2.351E-2</v>
       </c>
       <c r="I67">
         <f t="shared" si="4"/>
-        <v>4.5999999999999687E-2</v>
+        <v>4.799999999999973E-2</v>
       </c>
       <c r="K67">
         <v>16</v>
@@ -20624,11 +20624,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="H68">
-        <v>2.265E-2</v>
+        <v>2.1930000000000002E-2</v>
       </c>
       <c r="I68">
         <f t="shared" si="4"/>
-        <v>5.0400000000000209E-2</v>
+        <v>6.3200000000000145E-2</v>
       </c>
       <c r="K68">
         <v>16.25</v>
@@ -20668,11 +20668,11 @@
         <v>1.94</v>
       </c>
       <c r="H69">
-        <v>2.0920000000000001E-2</v>
+        <v>2.051E-2</v>
       </c>
       <c r="I69">
         <f t="shared" ref="I69:I76" si="10">(H68-H69)/(G69-G68)</f>
-        <v>6.9199999999999581E-2</v>
+        <v>5.679999999999974E-2</v>
       </c>
       <c r="K69">
         <v>16.5</v>
@@ -20712,11 +20712,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="H70">
-        <v>2.0049999999999998E-2</v>
+        <v>1.874E-2</v>
       </c>
       <c r="I70">
         <f t="shared" si="10"/>
-        <v>3.4800000000000234E-2</v>
+        <v>7.0800000000000279E-2</v>
       </c>
       <c r="K70">
         <v>16.75</v>
@@ -20756,11 +20756,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="H71">
-        <v>1.789E-2</v>
+        <v>1.7670000000000002E-2</v>
       </c>
       <c r="I71">
         <f t="shared" si="10"/>
-        <v>8.6400000000000254E-2</v>
+        <v>4.2800000000000074E-2</v>
       </c>
       <c r="K71">
         <v>17</v>
@@ -20800,11 +20800,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="H72">
-        <v>1.536E-2</v>
+        <v>1.453E-2</v>
       </c>
       <c r="I72">
         <f t="shared" si="10"/>
-        <v>0.10120000000000033</v>
+        <v>0.12560000000000054</v>
       </c>
       <c r="K72">
         <v>17.25</v>
@@ -20844,11 +20844,11 @@
         <v>2.04</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>7.8700000000000003E-3</v>
       </c>
       <c r="I73">
         <f t="shared" si="10"/>
-        <v>0.61439999999999129</v>
+        <v>0.2663999999999962</v>
       </c>
       <c r="K73">
         <v>17.5</v>
@@ -20888,11 +20888,11 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>5.9699999999999996E-3</v>
       </c>
       <c r="I74">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7.600000000000029E-2</v>
       </c>
       <c r="K74">
         <v>17.75</v>
@@ -20932,11 +20932,11 @@
         <v>2.09</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>2.0799999999999998E-3</v>
       </c>
       <c r="I75">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.15560000000000054</v>
       </c>
       <c r="K75">
         <v>18</v>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="I76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>8.3200000000000288E-2</v>
       </c>
       <c r="K76">
         <v>18.25</v>
@@ -21616,11 +21616,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="C5">
-        <v>0.99458999999999997</v>
+        <v>0.99451999999999996</v>
       </c>
       <c r="D5">
         <f t="shared" ref="D5:D68" si="1">(C4-C5)/(B5-B4)</f>
-        <v>0.21640000000000131</v>
+        <v>0.21920000000000192</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -21632,11 +21632,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="C6">
-        <v>0.97867999999999999</v>
+        <v>0.97884000000000004</v>
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
-        <v>0.63639999999999863</v>
+        <v>0.62719999999999609</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -21648,11 +21648,11 @@
         <v>0.39</v>
       </c>
       <c r="C7">
-        <v>0.96057000000000003</v>
+        <v>0.96077000000000001</v>
       </c>
       <c r="D7">
         <f t="shared" si="1"/>
-        <v>0.72439999999999771</v>
+        <v>0.72280000000000055</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -21664,11 +21664,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="C8">
-        <v>0.94106999999999996</v>
+        <v>0.94137000000000004</v>
       </c>
       <c r="D8">
         <f t="shared" si="1"/>
-        <v>0.78000000000000225</v>
+        <v>0.77599999999999825</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -21680,11 +21680,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="C9">
-        <v>0.92081000000000002</v>
+        <v>0.92098000000000002</v>
       </c>
       <c r="D9">
         <f t="shared" si="1"/>
-        <v>0.81039999999999712</v>
+        <v>0.81559999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -21696,11 +21696,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="C10">
-        <v>0.90036000000000005</v>
+        <v>0.90049000000000001</v>
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>0.81799999999999984</v>
+        <v>0.81960000000000144</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -21712,11 +21712,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="C11">
-        <v>0.87960000000000005</v>
+        <v>0.87983</v>
       </c>
       <c r="D11">
         <f t="shared" si="1"/>
-        <v>0.83039999999999925</v>
+        <v>0.82639999999999969</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -21728,11 +21728,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="C12">
-        <v>0.85873999999999995</v>
+        <v>0.85919000000000001</v>
       </c>
       <c r="D12">
         <f t="shared" si="1"/>
-        <v>0.83440000000000514</v>
+        <v>0.82560000000000078</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -21744,11 +21744,11 @@
         <v>0.54</v>
       </c>
       <c r="C13">
-        <v>0.83789999999999998</v>
+        <v>0.83831999999999995</v>
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
-        <v>0.83359999999999801</v>
+        <v>0.83480000000000143</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -21760,11 +21760,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="C14">
-        <v>0.81620000000000004</v>
+        <v>0.81684999999999997</v>
       </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>0.86799999999999689</v>
+        <v>0.85879999999999879</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -21776,11 +21776,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="C15">
-        <v>0.79430999999999996</v>
+        <v>0.79527999999999999</v>
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>0.87560000000000227</v>
+        <v>0.86279999999999835</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -21792,11 +21792,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="C16">
-        <v>0.77329000000000003</v>
+        <v>0.77385999999999999</v>
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
-        <v>0.8408000000000001</v>
+        <v>0.85680000000000278</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -21808,11 +21808,11 @@
         <v>0.64</v>
       </c>
       <c r="C17">
-        <v>0.75244999999999995</v>
+        <v>0.75261</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>0.83360000000000245</v>
+        <v>0.84999999999999887</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -21824,11 +21824,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="C18">
-        <v>0.73068</v>
+        <v>0.73133000000000004</v>
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
-        <v>0.87079999999999746</v>
+        <v>0.85119999999999785</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -21840,11 +21840,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="C19">
-        <v>0.70828000000000002</v>
+        <v>0.70909</v>
       </c>
       <c r="D19">
         <f t="shared" si="1"/>
-        <v>0.89599999999999824</v>
+        <v>0.88960000000000072</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -21856,11 +21856,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="C20">
-        <v>0.68652999999999997</v>
+        <v>0.68732000000000004</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.87000000000000111</v>
+        <v>0.87079999999999746</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -21872,11 +21872,11 @@
         <v>0.74</v>
       </c>
       <c r="C21">
-        <v>0.66439999999999999</v>
+        <v>0.66598999999999997</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0.88520000000000243</v>
+        <v>0.85320000000000584</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -21888,11 +21888,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="C22">
-        <v>0.64183999999999997</v>
+        <v>0.64359999999999995</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0.9024000000000002</v>
+        <v>0.89560000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -21904,11 +21904,11 @@
         <v>0.79</v>
       </c>
       <c r="C23">
-        <v>0.61999000000000004</v>
+        <v>0.62207000000000001</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0.87399999999999622</v>
+        <v>0.86119999999999675</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -21920,11 +21920,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="C24">
-        <v>0.59782999999999997</v>
+        <v>0.59884000000000004</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0.88640000000000196</v>
+        <v>0.92919999999999814</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -21936,11 +21936,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="C25">
-        <v>0.57533999999999996</v>
+        <v>0.57691999999999999</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.89959999999999962</v>
+        <v>0.87680000000000125</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -21952,11 +21952,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="C26">
-        <v>0.55220000000000002</v>
+        <v>0.55462</v>
       </c>
       <c r="D26">
         <f t="shared" si="1"/>
-        <v>0.92560000000000087</v>
+        <v>0.89200000000000268</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -21968,11 +21968,11 @@
         <v>0.89</v>
       </c>
       <c r="C27">
-        <v>0.53008999999999995</v>
+        <v>0.53288000000000002</v>
       </c>
       <c r="D27">
         <f t="shared" si="1"/>
-        <v>0.88440000000000218</v>
+        <v>0.86959999999999849</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -21984,11 +21984,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="C28">
-        <v>0.50912999999999997</v>
+        <v>0.51078999999999997</v>
       </c>
       <c r="D28">
         <f t="shared" si="1"/>
-        <v>0.83839999999999837</v>
+        <v>0.88360000000000138</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -22000,11 +22000,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="C29">
-        <v>0.48691000000000001</v>
+        <v>0.48836000000000002</v>
       </c>
       <c r="D29">
         <f t="shared" si="1"/>
-        <v>0.8887999999999977</v>
+        <v>0.89719999999999722</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -22016,11 +22016,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="C30">
-        <v>0.46562999999999999</v>
+        <v>0.46644000000000002</v>
       </c>
       <c r="D30">
         <f t="shared" si="1"/>
-        <v>0.85120000000000007</v>
+        <v>0.87679999999999902</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -22032,11 +22032,11 @@
         <v>0.99</v>
       </c>
       <c r="C31">
-        <v>0.44438</v>
+        <v>0.44485000000000002</v>
       </c>
       <c r="D31">
         <f t="shared" si="1"/>
-        <v>0.85000000000000264</v>
+        <v>0.86360000000000303</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -22048,11 +22048,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="C32">
-        <v>0.42377999999999999</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="D32">
         <f t="shared" si="1"/>
-        <v>0.82399999999999585</v>
+        <v>0.81399999999999706</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -22064,11 +22064,11 @@
         <v>1.04</v>
       </c>
       <c r="C33">
-        <v>0.40337000000000001</v>
+        <v>0.40405000000000002</v>
       </c>
       <c r="D33">
         <f t="shared" si="1"/>
-        <v>0.81640000000000224</v>
+        <v>0.81800000000000161</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -22080,11 +22080,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="C34">
-        <v>0.38228000000000001</v>
+        <v>0.38413999999999998</v>
       </c>
       <c r="D34">
         <f t="shared" si="1"/>
-        <v>0.8436000000000029</v>
+        <v>0.79640000000000433</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -22096,11 +22096,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="C35">
-        <v>0.36359999999999998</v>
+        <v>0.36514999999999997</v>
       </c>
       <c r="D35">
         <f t="shared" si="1"/>
-        <v>0.7471999999999972</v>
+        <v>0.75959999999999628</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -22112,11 +22112,11 @@
         <v>1.115</v>
       </c>
       <c r="C36">
-        <v>0.34447</v>
+        <v>0.34588999999999998</v>
       </c>
       <c r="D36">
         <f t="shared" si="1"/>
-        <v>0.76520000000000188</v>
+        <v>0.77040000000000275</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -22128,11 +22128,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="C37">
-        <v>0.32571</v>
+        <v>0.32683000000000001</v>
       </c>
       <c r="D37">
         <f t="shared" si="1"/>
-        <v>0.75039999999999596</v>
+        <v>0.76239999999999453</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -22144,11 +22144,11 @@
         <v>1.165</v>
       </c>
       <c r="C38">
-        <v>0.30769999999999997</v>
+        <v>0.30853000000000003</v>
       </c>
       <c r="D38">
         <f t="shared" si="1"/>
-        <v>0.72040000000000359</v>
+        <v>0.73200000000000187</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -22160,11 +22160,11 @@
         <v>1.19</v>
       </c>
       <c r="C39">
-        <v>0.29013</v>
+        <v>0.28928999999999999</v>
       </c>
       <c r="D39">
         <f t="shared" si="1"/>
-        <v>0.70280000000000142</v>
+        <v>0.76960000000000417</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -22176,11 +22176,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="C40">
-        <v>0.27145999999999998</v>
+        <v>0.27139999999999997</v>
       </c>
       <c r="D40">
         <f t="shared" si="1"/>
-        <v>0.7467999999999968</v>
+        <v>0.71559999999999691</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -22192,11 +22192,11 @@
         <v>1.24</v>
       </c>
       <c r="C41">
-        <v>0.25273000000000001</v>
+        <v>0.25509999999999999</v>
       </c>
       <c r="D41">
         <f t="shared" si="1"/>
-        <v>0.74920000000000142</v>
+        <v>0.65200000000000158</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -22208,11 +22208,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="C42">
-        <v>0.23733000000000001</v>
+        <v>0.23845</v>
       </c>
       <c r="D42">
         <f t="shared" si="1"/>
-        <v>0.61599999999999655</v>
+        <v>0.66599999999999637</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -22224,11 +22224,11 @@
         <v>1.29</v>
       </c>
       <c r="C43">
-        <v>0.22248999999999999</v>
+        <v>0.22289</v>
       </c>
       <c r="D43">
         <f t="shared" si="1"/>
-        <v>0.5936000000000029</v>
+        <v>0.62240000000000184</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -22240,11 +22240,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="C44">
-        <v>0.20765</v>
+        <v>0.20718</v>
       </c>
       <c r="D44">
         <f t="shared" si="1"/>
-        <v>0.59360000000000179</v>
+        <v>0.62840000000000229</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -22256,11 +22256,11 @@
         <v>1.34</v>
       </c>
       <c r="C45">
-        <v>0.19286</v>
+        <v>0.19419</v>
       </c>
       <c r="D45">
         <f t="shared" si="1"/>
-        <v>0.5915999999999968</v>
+        <v>0.51959999999999729</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -22272,11 +22272,11 @@
         <v>1.365</v>
       </c>
       <c r="C46">
-        <v>0.17979999999999999</v>
+        <v>0.18040999999999999</v>
       </c>
       <c r="D46">
         <f t="shared" si="1"/>
-        <v>0.52240000000000253</v>
+        <v>0.55120000000000258</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -22288,11 +22288,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="C47">
-        <v>0.16800000000000001</v>
+        <v>0.16939000000000001</v>
       </c>
       <c r="D47">
         <f t="shared" si="1"/>
-        <v>0.47199999999999659</v>
+        <v>0.44079999999999664</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -22304,11 +22304,11 @@
         <v>1.415</v>
       </c>
       <c r="C48">
-        <v>0.15620999999999999</v>
+        <v>0.15767</v>
       </c>
       <c r="D48">
         <f t="shared" si="1"/>
-        <v>0.47160000000000257</v>
+        <v>0.46880000000000199</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -22320,11 +22320,11 @@
         <v>1.44</v>
       </c>
       <c r="C49">
-        <v>0.14399999999999999</v>
+        <v>0.14473</v>
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>0.48840000000000167</v>
+        <v>0.51760000000000217</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -22336,11 +22336,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="C50">
-        <v>0.13511999999999999</v>
+        <v>0.13481000000000001</v>
       </c>
       <c r="D50">
         <f t="shared" si="1"/>
-        <v>0.35519999999999807</v>
+        <v>0.39679999999999727</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -22352,11 +22352,11 @@
         <v>1.49</v>
       </c>
       <c r="C51">
-        <v>0.12418999999999999</v>
+        <v>0.12586</v>
       </c>
       <c r="D51">
         <f t="shared" si="1"/>
-        <v>0.43720000000000137</v>
+        <v>0.35800000000000182</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -22368,11 +22368,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="C52">
-        <v>0.11550000000000001</v>
+        <v>0.11734</v>
       </c>
       <c r="D52">
         <f t="shared" si="1"/>
-        <v>0.34759999999999774</v>
+        <v>0.34079999999999816</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -22384,11 +22384,11 @@
         <v>1.54</v>
       </c>
       <c r="C53">
-        <v>0.10788</v>
+        <v>0.10847</v>
       </c>
       <c r="D53">
         <f t="shared" si="1"/>
-        <v>0.30480000000000118</v>
+        <v>0.35480000000000139</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -22400,11 +22400,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="C54">
-        <v>9.9580000000000002E-2</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="D54">
         <f t="shared" si="1"/>
-        <v>0.33200000000000124</v>
+        <v>0.36680000000000118</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -22416,11 +22416,11 @@
         <v>1.59</v>
       </c>
       <c r="C55">
-        <v>9.0980000000000005E-2</v>
+        <v>9.2149999999999996E-2</v>
       </c>
       <c r="D55">
         <f t="shared" si="1"/>
-        <v>0.34399999999999803</v>
+        <v>0.28599999999999864</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -22432,11 +22432,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="C56">
-        <v>8.4669999999999995E-2</v>
+        <v>8.4699999999999998E-2</v>
       </c>
       <c r="D56">
         <f t="shared" si="1"/>
-        <v>0.25240000000000357</v>
+        <v>0.29800000000000365</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -22448,11 +22448,11 @@
         <v>1.64</v>
       </c>
       <c r="C57">
-        <v>7.6259999999999994E-2</v>
+        <v>7.5319999999999998E-2</v>
       </c>
       <c r="D57">
         <f t="shared" si="1"/>
-        <v>0.33639999999999826</v>
+        <v>0.37519999999999798</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -22464,11 +22464,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="C58">
-        <v>6.7750000000000005E-2</v>
+        <v>6.9019999999999998E-2</v>
       </c>
       <c r="D58">
         <f t="shared" si="1"/>
-        <v>0.34040000000000081</v>
+        <v>0.25200000000000089</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -22480,11 +22480,11 @@
         <v>1.69</v>
       </c>
       <c r="C59">
-        <v>6.021E-2</v>
+        <v>6.2330000000000003E-2</v>
       </c>
       <c r="D59">
         <f t="shared" si="1"/>
-        <v>0.30159999999999859</v>
+        <v>0.26759999999999834</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -22496,11 +22496,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="C60">
-        <v>5.4120000000000001E-2</v>
+        <v>5.3839999999999999E-2</v>
       </c>
       <c r="D60">
         <f t="shared" si="1"/>
-        <v>0.24360000000000079</v>
+        <v>0.3396000000000014</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -22512,11 +22512,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="C61">
-        <v>4.6339999999999999E-2</v>
+        <v>4.6780000000000002E-2</v>
       </c>
       <c r="D61">
         <f t="shared" si="1"/>
-        <v>0.3112000000000012</v>
+        <v>0.28240000000000087</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -22528,11 +22528,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="C62">
-        <v>3.9129999999999998E-2</v>
+        <v>4.0989999999999999E-2</v>
       </c>
       <c r="D62">
         <f t="shared" si="1"/>
-        <v>0.28839999999999849</v>
+        <v>0.23159999999999892</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -22544,11 +22544,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="C63">
-        <v>3.3599999999999998E-2</v>
+        <v>3.388E-2</v>
       </c>
       <c r="D63">
         <f t="shared" si="1"/>
-        <v>0.22120000000000078</v>
+        <v>0.28440000000000093</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -22560,11 +22560,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="C64">
-        <v>2.6270000000000002E-2</v>
+        <v>2.8080000000000001E-2</v>
       </c>
       <c r="D64">
         <f t="shared" si="1"/>
-        <v>0.2931999999999983</v>
+        <v>0.23199999999999874</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -22576,11 +22576,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="C65">
-        <v>2.2790000000000001E-2</v>
+        <v>2.4080000000000001E-2</v>
       </c>
       <c r="D65">
         <f t="shared" si="1"/>
-        <v>0.13920000000000052</v>
+        <v>0.16000000000000056</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -22592,11 +22592,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="C66">
-        <v>1.753E-2</v>
+        <v>1.7909999999999999E-2</v>
       </c>
       <c r="D66">
         <f t="shared" si="1"/>
-        <v>0.21040000000000078</v>
+        <v>0.24680000000000096</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -22608,11 +22608,11 @@
         <v>1.89</v>
       </c>
       <c r="C67">
-        <v>1.3129999999999999E-2</v>
+        <v>1.325E-2</v>
       </c>
       <c r="D67">
         <f t="shared" si="1"/>
-        <v>0.1759999999999991</v>
+        <v>0.18639999999999898</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -22624,11 +22624,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="C68">
-        <v>8.6700000000000006E-3</v>
+        <v>7.4900000000000001E-3</v>
       </c>
       <c r="D68">
         <f t="shared" si="1"/>
-        <v>0.17840000000000059</v>
+        <v>0.2304000000000008</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -22640,11 +22640,11 @@
         <v>1.94</v>
       </c>
       <c r="C69">
-        <v>5.2399999999999999E-3</v>
+        <v>6.6499999999999997E-3</v>
       </c>
       <c r="D69">
         <f t="shared" ref="D69:D76" si="3">(C68-C69)/(B69-B68)</f>
-        <v>0.13719999999999929</v>
+        <v>3.3599999999999838E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -22656,11 +22656,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="C70">
-        <v>4.2100000000000002E-3</v>
+        <v>5.6100000000000004E-3</v>
       </c>
       <c r="D70">
         <f t="shared" si="3"/>
-        <v>4.1200000000000132E-2</v>
+        <v>4.1600000000000116E-2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -22672,11 +22672,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="C71">
-        <v>2.8700000000000002E-3</v>
+        <v>2.96E-3</v>
       </c>
       <c r="D71">
         <f t="shared" si="3"/>
-        <v>5.3600000000000189E-2</v>
+        <v>0.1060000000000004</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -22688,11 +22688,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="C72">
-        <v>1.6800000000000001E-3</v>
+        <v>2.2799999999999999E-3</v>
       </c>
       <c r="D72">
         <f t="shared" si="3"/>
-        <v>4.760000000000017E-2</v>
+        <v>2.7200000000000099E-2</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -22704,11 +22704,11 @@
         <v>2.04</v>
       </c>
       <c r="C73">
-        <v>1.2800000000000001E-3</v>
+        <v>1.6800000000000001E-3</v>
       </c>
       <c r="D73">
         <f t="shared" si="3"/>
-        <v>1.5999999999999771E-2</v>
+        <v>2.3999999999999654E-2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -22720,11 +22720,11 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="C74">
-        <v>6.4000000000000005E-4</v>
+        <v>6.6E-4</v>
       </c>
       <c r="D74">
         <f t="shared" si="3"/>
-        <v>2.5600000000000091E-2</v>
+        <v>4.0800000000000149E-2</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="D75">
         <f t="shared" si="3"/>
-        <v>2.5600000000000091E-2</v>
+        <v>2.6400000000000094E-2</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23026,11 +23026,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="C7">
-        <v>0.99458999999999997</v>
+        <v>0.99451999999999996</v>
       </c>
       <c r="D7">
         <f t="shared" ref="D7:D70" si="4">(C6-C7)/(B7-B6)</f>
-        <v>0.21640000000000131</v>
+        <v>0.21920000000000192</v>
       </c>
       <c r="F7">
         <v>3.4</v>
@@ -23040,11 +23040,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="H7">
-        <v>0.99724999999999997</v>
+        <v>0.99722999999999995</v>
       </c>
       <c r="I7">
         <f t="shared" ref="I7:I70" si="5">(H6-H7)/(G7-G6)</f>
-        <v>0.11000000000000136</v>
+        <v>0.11080000000000216</v>
       </c>
       <c r="K7">
         <v>3.4</v>
@@ -23054,11 +23054,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="M7">
-        <v>0.99682000000000004</v>
+        <v>0.99677000000000004</v>
       </c>
       <c r="N7">
         <f t="shared" ref="N7:N70" si="6">(M6-M7)/(L7-L6)</f>
-        <v>0.12719999999999859</v>
+        <v>0.12919999999999837</v>
       </c>
       <c r="P7">
         <v>3.4</v>
@@ -23068,11 +23068,11 @@
         <v>0.33999999999999997</v>
       </c>
       <c r="R7">
-        <v>0.99758000000000002</v>
+        <v>0.99763999999999997</v>
       </c>
       <c r="S7">
         <f t="shared" ref="S7:S70" si="7">(R6-R7)/(Q7-Q6)</f>
-        <v>9.6799999999999234E-2</v>
+        <v>9.4400000000001275E-2</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -23084,11 +23084,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="C8">
-        <v>0.97867999999999999</v>
+        <v>0.97884000000000004</v>
       </c>
       <c r="D8">
         <f t="shared" si="4"/>
-        <v>0.63639999999999863</v>
+        <v>0.62719999999999609</v>
       </c>
       <c r="F8">
         <v>3.65</v>
@@ -23098,11 +23098,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="H8">
-        <v>0.98980999999999997</v>
+        <v>0.98982000000000003</v>
       </c>
       <c r="I8">
         <f t="shared" si="5"/>
-        <v>0.29759999999999981</v>
+        <v>0.29639999999999639</v>
       </c>
       <c r="K8">
         <v>3.65</v>
@@ -23112,11 +23112,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="M8">
-        <v>0.98787000000000003</v>
+        <v>0.98770000000000002</v>
       </c>
       <c r="N8">
         <f t="shared" si="6"/>
-        <v>0.35800000000000021</v>
+        <v>0.36280000000000057</v>
       </c>
       <c r="P8">
         <v>3.65</v>
@@ -23126,11 +23126,11 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="R8">
-        <v>0.99141999999999997</v>
+        <v>0.99136000000000002</v>
       </c>
       <c r="S8">
         <f t="shared" si="7"/>
-        <v>0.24640000000000195</v>
+        <v>0.25119999999999787</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -23142,11 +23142,11 @@
         <v>0.39</v>
       </c>
       <c r="C9">
-        <v>0.96057000000000003</v>
+        <v>0.96077000000000001</v>
       </c>
       <c r="D9">
         <f t="shared" si="4"/>
-        <v>0.72439999999999771</v>
+        <v>0.72280000000000055</v>
       </c>
       <c r="F9">
         <v>3.9</v>
@@ -23156,11 +23156,11 @@
         <v>0.39</v>
       </c>
       <c r="H9">
-        <v>0.98197999999999996</v>
+        <v>0.98194000000000004</v>
       </c>
       <c r="I9">
         <f t="shared" si="5"/>
-        <v>0.31319999999999987</v>
+        <v>0.31519999999999965</v>
       </c>
       <c r="K9">
         <v>3.9</v>
@@ -23170,11 +23170,11 @@
         <v>0.39</v>
       </c>
       <c r="M9">
-        <v>0.97819</v>
+        <v>0.97782999999999998</v>
       </c>
       <c r="N9">
         <f t="shared" si="6"/>
-        <v>0.38720000000000054</v>
+        <v>0.39480000000000148</v>
       </c>
       <c r="P9">
         <v>3.9</v>
@@ -23184,11 +23184,11 @@
         <v>0.39</v>
       </c>
       <c r="R9">
-        <v>0.98495999999999995</v>
+        <v>0.98487999999999998</v>
       </c>
       <c r="S9">
         <f t="shared" si="7"/>
-        <v>0.25840000000000063</v>
+        <v>0.25920000000000143</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -23200,11 +23200,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="C10">
-        <v>0.94106999999999996</v>
+        <v>0.94137000000000004</v>
       </c>
       <c r="D10">
         <f t="shared" si="4"/>
-        <v>0.78000000000000225</v>
+        <v>0.77599999999999825</v>
       </c>
       <c r="F10">
         <v>4.1500000000000004</v>
@@ -23214,11 +23214,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="H10">
-        <v>0.97380999999999995</v>
+        <v>0.97370999999999996</v>
       </c>
       <c r="I10">
         <f t="shared" si="5"/>
-        <v>0.32680000000000015</v>
+        <v>0.32920000000000255</v>
       </c>
       <c r="K10">
         <v>4.1500000000000004</v>
@@ -23228,11 +23228,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="M10">
-        <v>0.96818000000000004</v>
+        <v>0.96791000000000005</v>
       </c>
       <c r="N10">
         <f t="shared" si="6"/>
-        <v>0.4003999999999982</v>
+        <v>0.39679999999999682</v>
       </c>
       <c r="P10">
         <v>4.1500000000000004</v>
@@ -23242,11 +23242,11 @@
         <v>0.41500000000000004</v>
       </c>
       <c r="R10">
-        <v>0.97865000000000002</v>
+        <v>0.97833000000000003</v>
       </c>
       <c r="S10">
         <f t="shared" si="7"/>
-        <v>0.25239999999999685</v>
+        <v>0.26199999999999757</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -23258,11 +23258,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="C11">
-        <v>0.92081000000000002</v>
+        <v>0.92098000000000002</v>
       </c>
       <c r="D11">
         <f t="shared" si="4"/>
-        <v>0.81039999999999712</v>
+        <v>0.81559999999999999</v>
       </c>
       <c r="F11">
         <v>4.4000000000000004</v>
@@ -23272,11 +23272,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="H11">
-        <v>0.96552000000000004</v>
+        <v>0.96514999999999995</v>
       </c>
       <c r="I11">
         <f t="shared" si="5"/>
-        <v>0.33159999999999606</v>
+        <v>0.3424000000000002</v>
       </c>
       <c r="K11">
         <v>4.4000000000000004</v>
@@ -23286,11 +23286,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="M11">
-        <v>0.95847000000000004</v>
+        <v>0.95818999999999999</v>
       </c>
       <c r="N11">
         <f t="shared" si="6"/>
-        <v>0.38839999999999952</v>
+        <v>0.38880000000000214</v>
       </c>
       <c r="P11">
         <v>4.4000000000000004</v>
@@ -23300,11 +23300,11 @@
         <v>0.44000000000000006</v>
       </c>
       <c r="R11">
-        <v>0.97233999999999998</v>
+        <v>0.97179000000000004</v>
       </c>
       <c r="S11">
         <f t="shared" si="7"/>
-        <v>0.25240000000000129</v>
+        <v>0.26159999999999939</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -23316,11 +23316,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="C12">
-        <v>0.90036000000000005</v>
+        <v>0.90049000000000001</v>
       </c>
       <c r="D12">
         <f t="shared" si="4"/>
-        <v>0.81799999999999984</v>
+        <v>0.81960000000000144</v>
       </c>
       <c r="F12">
         <v>4.6500000000000004</v>
@@ -23330,11 +23330,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="H12">
-        <v>0.95672999999999997</v>
+        <v>0.95635000000000003</v>
       </c>
       <c r="I12">
         <f t="shared" si="5"/>
-        <v>0.35160000000000347</v>
+        <v>0.3519999999999972</v>
       </c>
       <c r="K12">
         <v>4.6500000000000004</v>
@@ -23344,11 +23344,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="M12">
-        <v>0.94935000000000003</v>
+        <v>0.94915000000000005</v>
       </c>
       <c r="N12">
         <f t="shared" si="6"/>
-        <v>0.36480000000000118</v>
+        <v>0.36159999999999798</v>
       </c>
       <c r="P12">
         <v>4.6500000000000004</v>
@@ -23358,11 +23358,11 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="R12">
-        <v>0.96601999999999999</v>
+        <v>0.96545000000000003</v>
       </c>
       <c r="S12">
         <f t="shared" si="7"/>
-        <v>0.25280000000000002</v>
+        <v>0.25360000000000082</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -23374,11 +23374,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="C13">
-        <v>0.87960000000000005</v>
+        <v>0.87983</v>
       </c>
       <c r="D13">
         <f t="shared" si="4"/>
-        <v>0.83039999999999925</v>
+        <v>0.82639999999999969</v>
       </c>
       <c r="F13">
         <v>4.9000000000000004</v>
@@ -23388,11 +23388,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="H13">
-        <v>0.94755999999999996</v>
+        <v>0.94721999999999995</v>
       </c>
       <c r="I13">
         <f t="shared" si="5"/>
-        <v>0.36680000000000013</v>
+        <v>0.36520000000000297</v>
       </c>
       <c r="K13">
         <v>4.9000000000000004</v>
@@ -23402,11 +23402,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="M13">
-        <v>0.94067999999999996</v>
+        <v>0.94038999999999995</v>
       </c>
       <c r="N13">
         <f t="shared" si="6"/>
-        <v>0.34680000000000233</v>
+        <v>0.35040000000000371</v>
       </c>
       <c r="P13">
         <v>4.9000000000000004</v>
@@ -23416,11 +23416,11 @@
         <v>0.49000000000000005</v>
       </c>
       <c r="R13">
-        <v>0.95974000000000004</v>
+        <v>0.95911000000000002</v>
       </c>
       <c r="S13">
         <f t="shared" si="7"/>
-        <v>0.25119999999999787</v>
+        <v>0.25360000000000027</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -23432,11 +23432,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="C14">
-        <v>0.85873999999999995</v>
+        <v>0.85919000000000001</v>
       </c>
       <c r="D14">
         <f t="shared" si="4"/>
-        <v>0.83440000000000514</v>
+        <v>0.82560000000000078</v>
       </c>
       <c r="F14">
         <v>5.15</v>
@@ -23446,11 +23446,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="H14">
-        <v>0.93813999999999997</v>
+        <v>0.93786999999999998</v>
       </c>
       <c r="I14">
         <f t="shared" si="5"/>
-        <v>0.37679999999999986</v>
+        <v>0.37399999999999928</v>
       </c>
       <c r="K14">
         <v>5.15</v>
@@ -23460,11 +23460,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="M14">
-        <v>0.93242999999999998</v>
+        <v>0.93220000000000003</v>
       </c>
       <c r="N14">
         <f t="shared" si="6"/>
-        <v>0.32999999999999963</v>
+        <v>0.32759999999999723</v>
       </c>
       <c r="P14">
         <v>5.15</v>
@@ -23474,11 +23474,11 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="R14">
-        <v>0.95321</v>
+        <v>0.95272999999999997</v>
       </c>
       <c r="S14">
         <f t="shared" si="7"/>
-        <v>0.26120000000000176</v>
+        <v>0.25520000000000242</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -23490,11 +23490,11 @@
         <v>0.54</v>
       </c>
       <c r="C15">
-        <v>0.83789999999999998</v>
+        <v>0.83831999999999995</v>
       </c>
       <c r="D15">
         <f t="shared" si="4"/>
-        <v>0.83359999999999801</v>
+        <v>0.83480000000000143</v>
       </c>
       <c r="F15">
         <v>5.4</v>
@@ -23504,11 +23504,11 @@
         <v>0.54</v>
       </c>
       <c r="H15">
-        <v>0.92849999999999999</v>
+        <v>0.92805000000000004</v>
       </c>
       <c r="I15">
         <f t="shared" si="5"/>
-        <v>0.38559999999999894</v>
+        <v>0.39279999999999726</v>
       </c>
       <c r="K15">
         <v>5.4</v>
@@ -23518,11 +23518,11 @@
         <v>0.54</v>
       </c>
       <c r="M15">
-        <v>0.92452999999999996</v>
+        <v>0.92434000000000005</v>
       </c>
       <c r="N15">
         <f t="shared" si="6"/>
-        <v>0.31600000000000045</v>
+        <v>0.31439999999999885</v>
       </c>
       <c r="P15">
         <v>5.4</v>
@@ -23532,11 +23532,11 @@
         <v>0.54</v>
       </c>
       <c r="R15">
-        <v>0.94677999999999995</v>
+        <v>0.94625999999999999</v>
       </c>
       <c r="S15">
         <f t="shared" si="7"/>
-        <v>0.25720000000000165</v>
+        <v>0.25879999999999881</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -23548,11 +23548,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="C16">
-        <v>0.81620000000000004</v>
+        <v>0.81684999999999997</v>
       </c>
       <c r="D16">
         <f t="shared" si="4"/>
-        <v>0.86799999999999689</v>
+        <v>0.85879999999999879</v>
       </c>
       <c r="F16">
         <v>5.65</v>
@@ -23562,11 +23562,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="H16">
-        <v>0.91832000000000003</v>
+        <v>0.91795000000000004</v>
       </c>
       <c r="I16">
         <f t="shared" si="5"/>
-        <v>0.40719999999999829</v>
+        <v>0.40399999999999958</v>
       </c>
       <c r="K16">
         <v>5.65</v>
@@ -23576,11 +23576,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="M16">
-        <v>0.91695000000000004</v>
+        <v>0.91662999999999994</v>
       </c>
       <c r="N16">
         <f t="shared" si="6"/>
-        <v>0.30319999999999653</v>
+        <v>0.30840000000000395</v>
       </c>
       <c r="P16">
         <v>5.65</v>
@@ -23590,11 +23590,11 @@
         <v>0.56500000000000006</v>
       </c>
       <c r="R16">
-        <v>0.94042999999999999</v>
+        <v>0.93994</v>
       </c>
       <c r="S16">
         <f t="shared" si="7"/>
-        <v>0.25399999999999845</v>
+        <v>0.25279999999999947</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -23606,11 +23606,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="C17">
-        <v>0.79430999999999996</v>
+        <v>0.79527999999999999</v>
       </c>
       <c r="D17">
         <f t="shared" si="4"/>
-        <v>0.87560000000000227</v>
+        <v>0.86279999999999835</v>
       </c>
       <c r="F17">
         <v>5.9</v>
@@ -23620,11 +23620,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="H17">
-        <v>0.90791999999999995</v>
+        <v>0.90759999999999996</v>
       </c>
       <c r="I17">
         <f t="shared" si="5"/>
-        <v>0.41600000000000265</v>
+        <v>0.41400000000000287</v>
       </c>
       <c r="K17">
         <v>5.9</v>
@@ -23634,11 +23634,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="M17">
-        <v>0.90952999999999995</v>
+        <v>0.90922000000000003</v>
       </c>
       <c r="N17">
         <f t="shared" si="6"/>
-        <v>0.29680000000000345</v>
+        <v>0.29639999999999639</v>
       </c>
       <c r="P17">
         <v>5.9</v>
@@ -23648,11 +23648,11 @@
         <v>0.59000000000000008</v>
       </c>
       <c r="R17">
-        <v>0.93396999999999997</v>
+        <v>0.93342999999999998</v>
       </c>
       <c r="S17">
         <f t="shared" si="7"/>
-        <v>0.25840000000000063</v>
+        <v>0.26040000000000041</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -23664,11 +23664,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="C18">
-        <v>0.77329000000000003</v>
+        <v>0.77385999999999999</v>
       </c>
       <c r="D18">
         <f t="shared" si="4"/>
-        <v>0.8408000000000001</v>
+        <v>0.85680000000000278</v>
       </c>
       <c r="F18">
         <v>6.15</v>
@@ -23678,11 +23678,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="H18">
-        <v>0.89686999999999995</v>
+        <v>0.89666999999999997</v>
       </c>
       <c r="I18">
         <f t="shared" si="5"/>
-        <v>0.44200000000000172</v>
+        <v>0.43720000000000137</v>
       </c>
       <c r="K18">
         <v>6.15</v>
@@ -23692,11 +23692,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="M18">
-        <v>0.90225</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="N18">
         <f t="shared" si="6"/>
-        <v>0.29119999999999918</v>
+        <v>0.28880000000000117</v>
       </c>
       <c r="P18">
         <v>6.15</v>
@@ -23706,11 +23706,11 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="R18">
-        <v>0.92739000000000005</v>
+        <v>0.92686000000000002</v>
       </c>
       <c r="S18">
         <f t="shared" si="7"/>
-        <v>0.26319999999999771</v>
+        <v>0.26279999999999953</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -23722,11 +23722,11 @@
         <v>0.64</v>
       </c>
       <c r="C19">
-        <v>0.75244999999999995</v>
+        <v>0.75261</v>
       </c>
       <c r="D19">
         <f t="shared" si="4"/>
-        <v>0.83360000000000245</v>
+        <v>0.84999999999999887</v>
       </c>
       <c r="F19">
         <v>6.4</v>
@@ -23736,11 +23736,11 @@
         <v>0.64</v>
       </c>
       <c r="H19">
-        <v>0.88527999999999996</v>
+        <v>0.88510999999999995</v>
       </c>
       <c r="I19">
         <f t="shared" si="5"/>
-        <v>0.46359999999999918</v>
+        <v>0.4624000000000002</v>
       </c>
       <c r="K19">
         <v>6.4</v>
@@ -23750,11 +23750,11 @@
         <v>0.64</v>
       </c>
       <c r="M19">
-        <v>0.89510000000000001</v>
+        <v>0.89498</v>
       </c>
       <c r="N19">
         <f t="shared" si="6"/>
-        <v>0.28599999999999931</v>
+        <v>0.28080000000000083</v>
       </c>
       <c r="P19">
         <v>6.4</v>
@@ -23764,11 +23764,11 @@
         <v>0.64</v>
       </c>
       <c r="R19">
-        <v>0.92090000000000005</v>
+        <v>0.92023999999999995</v>
       </c>
       <c r="S19">
         <f t="shared" si="7"/>
-        <v>0.25959999999999961</v>
+        <v>0.26480000000000259</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -23780,11 +23780,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="C20">
-        <v>0.73068</v>
+        <v>0.73133000000000004</v>
       </c>
       <c r="D20">
         <f t="shared" si="4"/>
-        <v>0.87079999999999746</v>
+        <v>0.85119999999999785</v>
       </c>
       <c r="F20">
         <v>6.65</v>
@@ -23794,11 +23794,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="H20">
-        <v>0.87346000000000001</v>
+        <v>0.87311000000000005</v>
       </c>
       <c r="I20">
         <f t="shared" si="5"/>
-        <v>0.47279999999999722</v>
+        <v>0.47999999999999554</v>
       </c>
       <c r="K20">
         <v>6.65</v>
@@ -23808,11 +23808,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="M20">
-        <v>0.88812000000000002</v>
+        <v>0.88788999999999996</v>
       </c>
       <c r="N20">
         <f t="shared" si="6"/>
-        <v>0.27919999999999923</v>
+        <v>0.28360000000000135</v>
       </c>
       <c r="P20">
         <v>6.65</v>
@@ -23822,11 +23822,11 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="R20">
-        <v>0.91434000000000004</v>
+        <v>0.91361999999999999</v>
       </c>
       <c r="S20">
         <f t="shared" si="7"/>
-        <v>0.26240000000000019</v>
+        <v>0.26479999999999815</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -23838,11 +23838,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="C21">
-        <v>0.70828000000000002</v>
+        <v>0.70909</v>
       </c>
       <c r="D21">
         <f t="shared" si="4"/>
-        <v>0.89599999999999824</v>
+        <v>0.88960000000000072</v>
       </c>
       <c r="F21">
         <v>6.9</v>
@@ -23852,11 +23852,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="H21">
-        <v>0.86073</v>
+        <v>0.86097999999999997</v>
       </c>
       <c r="I21">
         <f t="shared" si="5"/>
-        <v>0.50920000000000032</v>
+        <v>0.48520000000000296</v>
       </c>
       <c r="K21">
         <v>6.9</v>
@@ -23866,11 +23866,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="M21">
-        <v>0.88122</v>
+        <v>0.88083999999999996</v>
       </c>
       <c r="N21">
         <f t="shared" si="6"/>
-        <v>0.27600000000000047</v>
+        <v>0.28199999999999975</v>
       </c>
       <c r="P21">
         <v>6.9</v>
@@ -23880,11 +23880,11 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="R21">
-        <v>0.90763000000000005</v>
+        <v>0.90697000000000005</v>
       </c>
       <c r="S21">
         <f t="shared" si="7"/>
-        <v>0.26839999999999953</v>
+        <v>0.26599999999999713</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -23896,11 +23896,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="C22">
-        <v>0.68652999999999997</v>
+        <v>0.68732000000000004</v>
       </c>
       <c r="D22">
         <f t="shared" si="4"/>
-        <v>0.87000000000000111</v>
+        <v>0.87079999999999746</v>
       </c>
       <c r="F22">
         <v>7.15</v>
@@ -23910,11 +23910,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="H22">
-        <v>0.84821999999999997</v>
+        <v>0.84823999999999999</v>
       </c>
       <c r="I22">
         <f t="shared" si="5"/>
-        <v>0.5004000000000004</v>
+        <v>0.5095999999999985</v>
       </c>
       <c r="K22">
         <v>7.15</v>
@@ -23924,11 +23924,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="M22">
-        <v>0.87429999999999997</v>
+        <v>0.87375000000000003</v>
       </c>
       <c r="N22">
         <f t="shared" si="6"/>
-        <v>0.27680000000000127</v>
+        <v>0.28359999999999691</v>
       </c>
       <c r="P22">
         <v>7.15</v>
@@ -23938,11 +23938,11 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="R22">
-        <v>0.90068000000000004</v>
+        <v>0.90017999999999998</v>
       </c>
       <c r="S22">
         <f t="shared" si="7"/>
-        <v>0.27800000000000025</v>
+        <v>0.27160000000000273</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -23954,11 +23954,11 @@
         <v>0.74</v>
       </c>
       <c r="C23">
-        <v>0.66439999999999999</v>
+        <v>0.66598999999999997</v>
       </c>
       <c r="D23">
         <f t="shared" si="4"/>
-        <v>0.88520000000000243</v>
+        <v>0.85320000000000584</v>
       </c>
       <c r="F23">
         <v>7.4</v>
@@ -23968,11 +23968,11 @@
         <v>0.74</v>
       </c>
       <c r="H23">
-        <v>0.83499000000000001</v>
+        <v>0.83506999999999998</v>
       </c>
       <c r="I23">
         <f t="shared" si="5"/>
-        <v>0.52920000000000045</v>
+        <v>0.52680000000000249</v>
       </c>
       <c r="K23">
         <v>7.4</v>
@@ -23982,11 +23982,11 @@
         <v>0.74</v>
       </c>
       <c r="M23">
-        <v>0.86734999999999995</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="N23">
         <f t="shared" si="6"/>
-        <v>0.27800000000000147</v>
+        <v>0.27000000000000229</v>
       </c>
       <c r="P23">
         <v>7.4</v>
@@ -23996,11 +23996,11 @@
         <v>0.74</v>
       </c>
       <c r="R23">
-        <v>0.89393</v>
+        <v>0.89324000000000003</v>
       </c>
       <c r="S23">
         <f t="shared" si="7"/>
-        <v>0.27000000000000229</v>
+        <v>0.27759999999999885</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -24012,11 +24012,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="C24">
-        <v>0.64183999999999997</v>
+        <v>0.64359999999999995</v>
       </c>
       <c r="D24">
         <f t="shared" si="4"/>
-        <v>0.9024000000000002</v>
+        <v>0.89560000000000006</v>
       </c>
       <c r="F24">
         <v>7.65</v>
@@ -24026,11 +24026,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="H24">
-        <v>0.82167000000000001</v>
+        <v>0.82155</v>
       </c>
       <c r="I24">
         <f t="shared" si="5"/>
-        <v>0.5327999999999995</v>
+        <v>0.54079999999999862</v>
       </c>
       <c r="K24">
         <v>7.65</v>
@@ -24040,11 +24040,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="M24">
-        <v>0.86034999999999995</v>
+        <v>0.86016000000000004</v>
       </c>
       <c r="N24">
         <f t="shared" si="6"/>
-        <v>0.28000000000000003</v>
+        <v>0.27359999999999807</v>
       </c>
       <c r="P24">
         <v>7.65</v>
@@ -24054,11 +24054,11 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="R24">
-        <v>0.88687000000000005</v>
+        <v>0.88615999999999995</v>
       </c>
       <c r="S24">
         <f t="shared" si="7"/>
-        <v>0.28239999999999793</v>
+        <v>0.28320000000000317</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -24070,11 +24070,11 @@
         <v>0.79</v>
       </c>
       <c r="C25">
-        <v>0.61999000000000004</v>
+        <v>0.62207000000000001</v>
       </c>
       <c r="D25">
         <f t="shared" si="4"/>
-        <v>0.87399999999999622</v>
+        <v>0.86119999999999675</v>
       </c>
       <c r="F25">
         <v>7.9</v>
@@ -24084,11 +24084,11 @@
         <v>0.79</v>
       </c>
       <c r="H25">
-        <v>0.80754000000000004</v>
+        <v>0.80786000000000002</v>
       </c>
       <c r="I25">
         <f t="shared" si="5"/>
-        <v>0.56519999999999848</v>
+        <v>0.54759999999999875</v>
       </c>
       <c r="K25">
         <v>7.9</v>
@@ -24098,11 +24098,11 @@
         <v>0.79</v>
       </c>
       <c r="M25">
-        <v>0.85329999999999995</v>
+        <v>0.85313000000000005</v>
       </c>
       <c r="N25">
         <f t="shared" si="6"/>
-        <v>0.28199999999999975</v>
+        <v>0.28119999999999901</v>
       </c>
       <c r="P25">
         <v>7.9</v>
@@ -24112,11 +24112,11 @@
         <v>0.79</v>
       </c>
       <c r="R25">
-        <v>0.87975000000000003</v>
+        <v>0.87870000000000004</v>
       </c>
       <c r="S25">
         <f t="shared" si="7"/>
-        <v>0.28480000000000033</v>
+        <v>0.29839999999999617</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
@@ -24128,11 +24128,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="C26">
-        <v>0.59782999999999997</v>
+        <v>0.59884000000000004</v>
       </c>
       <c r="D26">
         <f t="shared" si="4"/>
-        <v>0.88640000000000196</v>
+        <v>0.92919999999999814</v>
       </c>
       <c r="F26">
         <v>8.15</v>
@@ -24142,11 +24142,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="H26">
-        <v>0.79366000000000003</v>
+        <v>0.79384999999999994</v>
       </c>
       <c r="I26">
         <f t="shared" si="5"/>
-        <v>0.55519999999999969</v>
+        <v>0.56040000000000267</v>
       </c>
       <c r="K26">
         <v>8.15</v>
@@ -24156,11 +24156,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="M26">
-        <v>0.84619999999999995</v>
+        <v>0.84611999999999998</v>
       </c>
       <c r="N26">
         <f t="shared" si="6"/>
-        <v>0.28399999999999953</v>
+        <v>0.28040000000000265</v>
       </c>
       <c r="P26">
         <v>8.15</v>
@@ -24170,11 +24170,11 @@
         <v>0.81500000000000006</v>
       </c>
       <c r="R26">
-        <v>0.87205999999999995</v>
+        <v>0.87080999999999997</v>
       </c>
       <c r="S26">
         <f t="shared" si="7"/>
-        <v>0.30760000000000315</v>
+        <v>0.31560000000000227</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -24186,11 +24186,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="C27">
-        <v>0.57533999999999996</v>
+        <v>0.57691999999999999</v>
       </c>
       <c r="D27">
         <f t="shared" si="4"/>
-        <v>0.89959999999999962</v>
+        <v>0.87680000000000125</v>
       </c>
       <c r="F27">
         <v>8.4</v>
@@ -24200,11 +24200,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="H27">
-        <v>0.77917999999999998</v>
+        <v>0.77924000000000004</v>
       </c>
       <c r="I27">
         <f t="shared" si="5"/>
-        <v>0.57920000000000138</v>
+        <v>0.58439999999999548</v>
       </c>
       <c r="K27">
         <v>8.4</v>
@@ -24214,11 +24214,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="M27">
-        <v>0.83918999999999999</v>
+        <v>0.83892</v>
       </c>
       <c r="N27">
         <f t="shared" si="6"/>
-        <v>0.28039999999999821</v>
+        <v>0.28799999999999909</v>
       </c>
       <c r="P27">
         <v>8.4</v>
@@ -24228,11 +24228,11 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="R27">
-        <v>0.86385000000000001</v>
+        <v>0.86265000000000003</v>
       </c>
       <c r="S27">
         <f t="shared" si="7"/>
-        <v>0.32839999999999731</v>
+        <v>0.32639999999999753</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -24244,11 +24244,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="C28">
-        <v>0.55220000000000002</v>
+        <v>0.55462</v>
       </c>
       <c r="D28">
         <f t="shared" si="4"/>
-        <v>0.92560000000000087</v>
+        <v>0.89200000000000268</v>
       </c>
       <c r="F28">
         <v>8.65</v>
@@ -24258,11 +24258,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="H28">
-        <v>0.76439000000000001</v>
+        <v>0.76419999999999999</v>
       </c>
       <c r="I28">
         <f t="shared" si="5"/>
-        <v>0.5916000000000009</v>
+        <v>0.60160000000000424</v>
       </c>
       <c r="K28">
         <v>8.65</v>
@@ -24272,11 +24272,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="M28">
-        <v>0.83164000000000005</v>
+        <v>0.83131999999999995</v>
       </c>
       <c r="N28">
         <f t="shared" si="6"/>
-        <v>0.30199999999999888</v>
+        <v>0.3040000000000031</v>
       </c>
       <c r="P28">
         <v>8.65</v>
@@ -24286,11 +24286,11 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="R28">
-        <v>0.85543000000000002</v>
+        <v>0.85406000000000004</v>
       </c>
       <c r="S28">
         <f t="shared" si="7"/>
-        <v>0.33680000000000054</v>
+        <v>0.34360000000000068</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -24302,11 +24302,11 @@
         <v>0.89</v>
       </c>
       <c r="C29">
-        <v>0.53008999999999995</v>
+        <v>0.53288000000000002</v>
       </c>
       <c r="D29">
         <f t="shared" si="4"/>
-        <v>0.88440000000000218</v>
+        <v>0.86959999999999849</v>
       </c>
       <c r="F29">
         <v>8.9</v>
@@ -24316,11 +24316,11 @@
         <v>0.89</v>
       </c>
       <c r="H29">
-        <v>0.74860000000000004</v>
+        <v>0.74829999999999997</v>
       </c>
       <c r="I29">
         <f t="shared" si="5"/>
-        <v>0.63159999999999827</v>
+        <v>0.63600000000000045</v>
       </c>
       <c r="K29">
         <v>8.9</v>
@@ -24330,11 +24330,11 @@
         <v>0.89</v>
       </c>
       <c r="M29">
-        <v>0.82367000000000001</v>
+        <v>0.82343</v>
       </c>
       <c r="N29">
         <f t="shared" si="6"/>
-        <v>0.31880000000000103</v>
+        <v>0.31559999999999783</v>
       </c>
       <c r="P29">
         <v>8.9</v>
@@ -24344,11 +24344,11 @@
         <v>0.89</v>
       </c>
       <c r="R29">
-        <v>0.84609000000000001</v>
+        <v>0.84492</v>
       </c>
       <c r="S29">
         <f t="shared" si="7"/>
-        <v>0.37360000000000027</v>
+        <v>0.36560000000000115</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -24360,11 +24360,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="C30">
-        <v>0.50912999999999997</v>
+        <v>0.51078999999999997</v>
       </c>
       <c r="D30">
         <f t="shared" si="4"/>
-        <v>0.83839999999999837</v>
+        <v>0.88360000000000138</v>
       </c>
       <c r="F30">
         <v>9.15</v>
@@ -24374,11 +24374,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="H30">
-        <v>0.73319999999999996</v>
+        <v>0.73311999999999999</v>
       </c>
       <c r="I30">
         <f t="shared" si="5"/>
-        <v>0.61600000000000266</v>
+        <v>0.6071999999999983</v>
       </c>
       <c r="K30">
         <v>9.15</v>
@@ -24388,11 +24388,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="M30">
-        <v>0.81549000000000005</v>
+        <v>0.81515000000000004</v>
       </c>
       <c r="N30">
         <f t="shared" si="6"/>
-        <v>0.32719999999999833</v>
+        <v>0.33119999999999788</v>
       </c>
       <c r="P30">
         <v>9.15</v>
@@ -24402,11 +24402,11 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="R30">
-        <v>0.83628000000000002</v>
+        <v>0.83528000000000002</v>
       </c>
       <c r="S30">
         <f t="shared" si="7"/>
-        <v>0.39239999999999908</v>
+        <v>0.38559999999999894</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
@@ -24418,11 +24418,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="C31">
-        <v>0.48691000000000001</v>
+        <v>0.48836000000000002</v>
       </c>
       <c r="D31">
         <f t="shared" si="4"/>
-        <v>0.8887999999999977</v>
+        <v>0.89719999999999722</v>
       </c>
       <c r="F31">
         <v>9.4</v>
@@ -24432,11 +24432,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="H31">
-        <v>0.71694999999999998</v>
+        <v>0.71702999999999995</v>
       </c>
       <c r="I31">
         <f t="shared" si="5"/>
-        <v>0.64999999999999891</v>
+        <v>0.64360000000000139</v>
       </c>
       <c r="K31">
         <v>9.4</v>
@@ -24446,11 +24446,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="M31">
-        <v>0.80669000000000002</v>
+        <v>0.80637999999999999</v>
       </c>
       <c r="N31">
         <f t="shared" si="6"/>
-        <v>0.35200000000000087</v>
+        <v>0.35080000000000189</v>
       </c>
       <c r="P31">
         <v>9.4</v>
@@ -24460,11 +24460,11 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="R31">
-        <v>0.82569999999999999</v>
+        <v>0.82457000000000003</v>
       </c>
       <c r="S31">
         <f t="shared" si="7"/>
-        <v>0.42320000000000096</v>
+        <v>0.4283999999999995</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
@@ -24476,11 +24476,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="C32">
-        <v>0.46562999999999999</v>
+        <v>0.46644000000000002</v>
       </c>
       <c r="D32">
         <f t="shared" si="4"/>
-        <v>0.85120000000000007</v>
+        <v>0.87679999999999902</v>
       </c>
       <c r="F32">
         <v>9.65</v>
@@ -24490,11 +24490,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="H32">
-        <v>0.70042000000000004</v>
+        <v>0.70021</v>
       </c>
       <c r="I32">
         <f t="shared" si="5"/>
-        <v>0.66119999999999679</v>
+        <v>0.67279999999999729</v>
       </c>
       <c r="K32">
         <v>9.65</v>
@@ -24504,11 +24504,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="M32">
-        <v>0.79754999999999998</v>
+        <v>0.79708999999999997</v>
       </c>
       <c r="N32">
         <f t="shared" si="6"/>
-        <v>0.36560000000000115</v>
+        <v>0.37160000000000049</v>
       </c>
       <c r="P32">
         <v>9.65</v>
@@ -24518,11 +24518,11 @@
         <v>0.96500000000000008</v>
       </c>
       <c r="R32">
-        <v>0.81450999999999996</v>
+        <v>0.81345999999999996</v>
       </c>
       <c r="S32">
         <f t="shared" si="7"/>
-        <v>0.44760000000000094</v>
+        <v>0.44440000000000218</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -24534,11 +24534,11 @@
         <v>0.99</v>
       </c>
       <c r="C33">
-        <v>0.44438</v>
+        <v>0.44485000000000002</v>
       </c>
       <c r="D33">
         <f t="shared" si="4"/>
-        <v>0.85000000000000264</v>
+        <v>0.86360000000000303</v>
       </c>
       <c r="F33">
         <v>9.9</v>
@@ -24548,11 +24548,11 @@
         <v>0.99</v>
       </c>
       <c r="H33">
-        <v>0.68344000000000005</v>
+        <v>0.68361000000000005</v>
       </c>
       <c r="I33">
         <f t="shared" si="5"/>
-        <v>0.67920000000000225</v>
+        <v>0.66400000000000026</v>
       </c>
       <c r="K33">
         <v>9.9</v>
@@ -24562,11 +24562,11 @@
         <v>0.99</v>
       </c>
       <c r="M33">
-        <v>0.78781999999999996</v>
+        <v>0.78693999999999997</v>
       </c>
       <c r="N33">
         <f t="shared" si="6"/>
-        <v>0.38920000000000204</v>
+        <v>0.40600000000000114</v>
       </c>
       <c r="P33">
         <v>9.9</v>
@@ -24576,11 +24576,11 @@
         <v>0.99</v>
       </c>
       <c r="R33">
-        <v>0.80252000000000001</v>
+        <v>0.80084999999999995</v>
       </c>
       <c r="S33">
         <f t="shared" si="7"/>
-        <v>0.47959999999999953</v>
+        <v>0.50440000000000218</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
@@ -24592,11 +24592,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="C34">
-        <v>0.42377999999999999</v>
+        <v>0.42449999999999999</v>
       </c>
       <c r="D34">
         <f t="shared" si="4"/>
-        <v>0.82399999999999585</v>
+        <v>0.81399999999999706</v>
       </c>
       <c r="F34">
         <v>10.15</v>
@@ -24606,11 +24606,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="H34">
-        <v>0.66635999999999995</v>
+        <v>0.66654999999999998</v>
       </c>
       <c r="I34">
         <f t="shared" si="5"/>
-        <v>0.68320000000000014</v>
+        <v>0.68239999999999934</v>
       </c>
       <c r="K34">
         <v>10.15</v>
@@ -24620,11 +24620,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="M34">
-        <v>0.77714000000000005</v>
+        <v>0.77649000000000001</v>
       </c>
       <c r="N34">
         <f t="shared" si="6"/>
-        <v>0.4271999999999942</v>
+        <v>0.41799999999999615</v>
       </c>
       <c r="P34">
         <v>10.15</v>
@@ -24634,11 +24634,11 @@
         <v>1.0150000000000001</v>
       </c>
       <c r="R34">
-        <v>0.78954999999999997</v>
+        <v>0.78779999999999994</v>
       </c>
       <c r="S34">
         <f t="shared" si="7"/>
-        <v>0.51879999999999871</v>
+        <v>0.52199999999999747</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
@@ -24650,11 +24650,11 @@
         <v>1.04</v>
       </c>
       <c r="C35">
-        <v>0.40337000000000001</v>
+        <v>0.40405000000000002</v>
       </c>
       <c r="D35">
         <f t="shared" si="4"/>
-        <v>0.81640000000000224</v>
+        <v>0.81800000000000161</v>
       </c>
       <c r="F35">
         <v>10.4</v>
@@ -24664,11 +24664,11 @@
         <v>1.04</v>
       </c>
       <c r="H35">
-        <v>0.64846999999999999</v>
+        <v>0.64915</v>
       </c>
       <c r="I35">
         <f t="shared" si="5"/>
-        <v>0.71560000000000101</v>
+        <v>0.69600000000000128</v>
       </c>
       <c r="K35">
         <v>10.4</v>
@@ -24678,11 +24678,11 @@
         <v>1.04</v>
       </c>
       <c r="M35">
-        <v>0.76605000000000001</v>
+        <v>0.76556000000000002</v>
       </c>
       <c r="N35">
         <f t="shared" si="6"/>
-        <v>0.44360000000000332</v>
+        <v>0.43720000000000137</v>
       </c>
       <c r="P35">
         <v>10.4</v>
@@ -24692,11 +24692,11 @@
         <v>1.04</v>
       </c>
       <c r="R35">
-        <v>0.77551000000000003</v>
+        <v>0.77371000000000001</v>
       </c>
       <c r="S35">
         <f t="shared" si="7"/>
-        <v>0.56159999999999966</v>
+        <v>0.56359999999999943</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -24708,11 +24708,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="C36">
-        <v>0.38228000000000001</v>
+        <v>0.38413999999999998</v>
       </c>
       <c r="D36">
         <f t="shared" si="4"/>
-        <v>0.8436000000000029</v>
+        <v>0.79640000000000433</v>
       </c>
       <c r="F36">
         <v>10.65</v>
@@ -24722,11 +24722,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="H36">
-        <v>0.63080999999999998</v>
+        <v>0.63126000000000004</v>
       </c>
       <c r="I36">
         <f t="shared" si="5"/>
-        <v>0.70640000000000291</v>
+        <v>0.71560000000000101</v>
       </c>
       <c r="K36">
         <v>10.65</v>
@@ -24736,11 +24736,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="M36">
-        <v>0.75453000000000003</v>
+        <v>0.75426000000000004</v>
       </c>
       <c r="N36">
         <f t="shared" si="6"/>
-        <v>0.4608000000000006</v>
+        <v>0.45200000000000068</v>
       </c>
       <c r="P36">
         <v>10.65</v>
@@ -24750,11 +24750,11 @@
         <v>1.0649999999999999</v>
       </c>
       <c r="R36">
-        <v>0.76043000000000005</v>
+        <v>0.75839000000000001</v>
       </c>
       <c r="S36">
         <f t="shared" si="7"/>
-        <v>0.6032000000000014</v>
+        <v>0.61280000000000223</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -24766,11 +24766,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="C37">
-        <v>0.36359999999999998</v>
+        <v>0.36514999999999997</v>
       </c>
       <c r="D37">
         <f t="shared" si="4"/>
-        <v>0.7471999999999972</v>
+        <v>0.75959999999999628</v>
       </c>
       <c r="F37">
         <v>10.9</v>
@@ -24780,11 +24780,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="H37">
-        <v>0.61336999999999997</v>
+        <v>0.61331999999999998</v>
       </c>
       <c r="I37">
         <f t="shared" si="5"/>
-        <v>0.69759999999999678</v>
+        <v>0.71759999999999891</v>
       </c>
       <c r="K37">
         <v>10.9</v>
@@ -24794,11 +24794,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="M37">
-        <v>0.74224999999999997</v>
+        <v>0.74175999999999997</v>
       </c>
       <c r="N37">
         <f t="shared" si="6"/>
-        <v>0.49120000000000014</v>
+        <v>0.5</v>
       </c>
       <c r="P37">
         <v>10.9</v>
@@ -24808,11 +24808,11 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="R37">
-        <v>0.74397000000000002</v>
+        <v>0.74160999999999999</v>
       </c>
       <c r="S37">
         <f t="shared" si="7"/>
-        <v>0.65839999999999765</v>
+        <v>0.67119999999999713</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
@@ -24824,11 +24824,11 @@
         <v>1.115</v>
       </c>
       <c r="C38">
-        <v>0.34447</v>
+        <v>0.34588999999999998</v>
       </c>
       <c r="D38">
         <f t="shared" si="4"/>
-        <v>0.76520000000000188</v>
+        <v>0.77040000000000275</v>
       </c>
       <c r="F38">
         <v>11.15</v>
@@ -24838,11 +24838,11 @@
         <v>1.115</v>
       </c>
       <c r="H38">
-        <v>0.59584000000000004</v>
+        <v>0.59416999999999998</v>
       </c>
       <c r="I38">
         <f t="shared" si="5"/>
-        <v>0.70119999999999982</v>
+        <v>0.76600000000000279</v>
       </c>
       <c r="K38">
         <v>11.15</v>
@@ -24852,11 +24852,11 @@
         <v>1.115</v>
       </c>
       <c r="M38">
-        <v>0.72914999999999996</v>
+        <v>0.72902</v>
       </c>
       <c r="N38">
         <f t="shared" si="6"/>
-        <v>0.52400000000000191</v>
+        <v>0.50960000000000072</v>
       </c>
       <c r="P38">
         <v>11.15</v>
@@ -24866,7 +24866,7 @@
         <v>1.115</v>
       </c>
       <c r="R38">
-        <v>0.72609000000000001</v>
+        <v>0.72372999999999998</v>
       </c>
       <c r="S38">
         <f t="shared" si="7"/>
@@ -24882,11 +24882,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="C39">
-        <v>0.32571</v>
+        <v>0.32683000000000001</v>
       </c>
       <c r="D39">
         <f t="shared" si="4"/>
-        <v>0.75039999999999596</v>
+        <v>0.76239999999999453</v>
       </c>
       <c r="F39">
         <v>11.4</v>
@@ -24896,11 +24896,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="H39">
-        <v>0.57698000000000005</v>
+        <v>0.57601999999999998</v>
       </c>
       <c r="I39">
         <f t="shared" si="5"/>
-        <v>0.75439999999999552</v>
+        <v>0.72599999999999609</v>
       </c>
       <c r="K39">
         <v>11.4</v>
@@ -24910,11 +24910,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="M39">
-        <v>0.71472999999999998</v>
+        <v>0.71423000000000003</v>
       </c>
       <c r="N39">
         <f t="shared" si="6"/>
-        <v>0.57679999999999643</v>
+        <v>0.59159999999999568</v>
       </c>
       <c r="P39">
         <v>11.4</v>
@@ -24924,11 +24924,11 @@
         <v>1.1400000000000001</v>
       </c>
       <c r="R39">
-        <v>0.70674000000000003</v>
+        <v>0.70413999999999999</v>
       </c>
       <c r="S39">
         <f t="shared" si="7"/>
-        <v>0.77399999999999503</v>
+        <v>0.78359999999999563</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
@@ -24940,11 +24940,11 @@
         <v>1.165</v>
       </c>
       <c r="C40">
-        <v>0.30769999999999997</v>
+        <v>0.30853000000000003</v>
       </c>
       <c r="D40">
         <f t="shared" si="4"/>
-        <v>0.72040000000000359</v>
+        <v>0.73200000000000187</v>
       </c>
       <c r="F40">
         <v>11.65</v>
@@ -24954,11 +24954,11 @@
         <v>1.165</v>
       </c>
       <c r="H40">
-        <v>0.55818999999999996</v>
+        <v>0.55830000000000002</v>
       </c>
       <c r="I40">
         <f t="shared" si="5"/>
-        <v>0.75160000000000604</v>
+        <v>0.70880000000000087</v>
       </c>
       <c r="K40">
         <v>11.65</v>
@@ -24968,11 +24968,11 @@
         <v>1.165</v>
       </c>
       <c r="M40">
-        <v>0.69891000000000003</v>
+        <v>0.69821</v>
       </c>
       <c r="N40">
         <f t="shared" si="6"/>
-        <v>0.63280000000000003</v>
+        <v>0.6408000000000037</v>
       </c>
       <c r="P40">
         <v>11.65</v>
@@ -24982,11 +24982,11 @@
         <v>1.165</v>
       </c>
       <c r="R40">
-        <v>0.68574000000000002</v>
+        <v>0.68201000000000001</v>
       </c>
       <c r="S40">
         <f t="shared" si="7"/>
-        <v>0.84000000000000374</v>
+        <v>0.88520000000000243</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -24998,11 +24998,11 @@
         <v>1.19</v>
       </c>
       <c r="C41">
-        <v>0.29013</v>
+        <v>0.28928999999999999</v>
       </c>
       <c r="D41">
         <f t="shared" si="4"/>
-        <v>0.70280000000000142</v>
+        <v>0.76960000000000417</v>
       </c>
       <c r="F41">
         <v>11.9</v>
@@ -25012,11 +25012,11 @@
         <v>1.19</v>
       </c>
       <c r="H41">
-        <v>0.53908</v>
+        <v>0.53793000000000002</v>
       </c>
       <c r="I41">
         <f t="shared" si="5"/>
-        <v>0.76440000000000108</v>
+        <v>0.81480000000000286</v>
       </c>
       <c r="K41">
         <v>11.9</v>
@@ -25026,11 +25026,11 @@
         <v>1.19</v>
       </c>
       <c r="M41">
-        <v>0.68130999999999997</v>
+        <v>0.68164000000000002</v>
       </c>
       <c r="N41">
         <f t="shared" si="6"/>
-        <v>0.70400000000000496</v>
+        <v>0.66280000000000128</v>
       </c>
       <c r="P41">
         <v>11.9</v>
@@ -25040,11 +25040,11 @@
         <v>1.19</v>
       </c>
       <c r="R41">
-        <v>0.66225000000000001</v>
+        <v>0.65778999999999999</v>
       </c>
       <c r="S41">
         <f t="shared" si="7"/>
-        <v>0.93960000000000377</v>
+        <v>0.96880000000000421</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
@@ -25056,11 +25056,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="C42">
-        <v>0.27145999999999998</v>
+        <v>0.27139999999999997</v>
       </c>
       <c r="D42">
         <f t="shared" si="4"/>
-        <v>0.7467999999999968</v>
+        <v>0.71559999999999691</v>
       </c>
       <c r="F42">
         <v>12.15</v>
@@ -25070,11 +25070,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="H42">
-        <v>0.51973000000000003</v>
+        <v>0.51892000000000005</v>
       </c>
       <c r="I42">
         <f t="shared" si="5"/>
-        <v>0.77399999999999503</v>
+        <v>0.76039999999999486</v>
       </c>
       <c r="K42">
         <v>12.15</v>
@@ -25084,11 +25084,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="M42">
-        <v>0.66312000000000004</v>
+        <v>0.66278000000000004</v>
       </c>
       <c r="N42">
         <f t="shared" si="6"/>
-        <v>0.72759999999999325</v>
+        <v>0.75439999999999552</v>
       </c>
       <c r="P42">
         <v>12.15</v>
@@ -25098,11 +25098,11 @@
         <v>1.2150000000000001</v>
       </c>
       <c r="R42">
-        <v>0.63658000000000003</v>
+        <v>0.63187000000000004</v>
       </c>
       <c r="S42">
         <f t="shared" si="7"/>
-        <v>1.0267999999999933</v>
+        <v>1.0367999999999922</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -25114,11 +25114,11 @@
         <v>1.24</v>
       </c>
       <c r="C43">
-        <v>0.25273000000000001</v>
+        <v>0.25509999999999999</v>
       </c>
       <c r="D43">
         <f t="shared" si="4"/>
-        <v>0.74920000000000142</v>
+        <v>0.65200000000000158</v>
       </c>
       <c r="F43">
         <v>12.4</v>
@@ -25128,11 +25128,11 @@
         <v>1.24</v>
       </c>
       <c r="H43">
-        <v>0.49990000000000001</v>
+        <v>0.49897000000000002</v>
       </c>
       <c r="I43">
         <f t="shared" si="5"/>
-        <v>0.79320000000000335</v>
+        <v>0.79800000000000382</v>
       </c>
       <c r="K43">
         <v>12.4</v>
@@ -25142,11 +25142,11 @@
         <v>1.24</v>
       </c>
       <c r="M43">
-        <v>0.64295999999999998</v>
+        <v>0.64229000000000003</v>
       </c>
       <c r="N43">
         <f t="shared" si="6"/>
-        <v>0.80640000000000556</v>
+        <v>0.81960000000000321</v>
       </c>
       <c r="P43">
         <v>12.4</v>
@@ -25156,11 +25156,11 @@
         <v>1.24</v>
       </c>
       <c r="R43">
-        <v>0.60579000000000005</v>
+        <v>0.60292000000000001</v>
       </c>
       <c r="S43">
         <f t="shared" si="7"/>
-        <v>1.2316000000000038</v>
+        <v>1.1580000000000055</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
@@ -25172,11 +25172,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="C44">
-        <v>0.23733000000000001</v>
+        <v>0.23845</v>
       </c>
       <c r="D44">
         <f t="shared" si="4"/>
-        <v>0.61599999999999655</v>
+        <v>0.66599999999999637</v>
       </c>
       <c r="F44">
         <v>12.65</v>
@@ -25186,11 +25186,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="H44">
-        <v>0.48020000000000002</v>
+        <v>0.47911999999999999</v>
       </c>
       <c r="I44">
         <f t="shared" si="5"/>
-        <v>0.78799999999999559</v>
+        <v>0.79399999999999715</v>
       </c>
       <c r="K44">
         <v>12.65</v>
@@ -25200,11 +25200,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="M44">
-        <v>0.62226000000000004</v>
+        <v>0.62126999999999999</v>
       </c>
       <c r="N44">
         <f t="shared" si="6"/>
-        <v>0.82799999999999319</v>
+        <v>0.84079999999999711</v>
       </c>
       <c r="P44">
         <v>12.65</v>
@@ -25214,11 +25214,11 @@
         <v>1.2650000000000001</v>
       </c>
       <c r="R44">
-        <v>0.57438999999999996</v>
+        <v>0.57206999999999997</v>
       </c>
       <c r="S44">
         <f t="shared" si="7"/>
-        <v>1.2559999999999971</v>
+        <v>1.2339999999999951</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -25230,11 +25230,11 @@
         <v>1.29</v>
       </c>
       <c r="C45">
-        <v>0.22248999999999999</v>
+        <v>0.22289</v>
       </c>
       <c r="D45">
         <f t="shared" si="4"/>
-        <v>0.5936000000000029</v>
+        <v>0.62240000000000184</v>
       </c>
       <c r="F45">
         <v>12.9</v>
@@ -25244,11 +25244,11 @@
         <v>1.29</v>
       </c>
       <c r="H45">
-        <v>0.46022999999999997</v>
+        <v>0.45949000000000001</v>
       </c>
       <c r="I45">
         <f t="shared" si="5"/>
-        <v>0.79880000000000462</v>
+        <v>0.78520000000000201</v>
       </c>
       <c r="K45">
         <v>12.9</v>
@@ -25258,11 +25258,11 @@
         <v>1.29</v>
       </c>
       <c r="M45">
-        <v>0.59904000000000002</v>
+        <v>0.59860000000000002</v>
       </c>
       <c r="N45">
         <f t="shared" si="6"/>
-        <v>0.92880000000000407</v>
+        <v>0.90680000000000194</v>
       </c>
       <c r="P45">
         <v>12.9</v>
@@ -25272,11 +25272,11 @@
         <v>1.29</v>
       </c>
       <c r="R45">
-        <v>0.54159000000000002</v>
+        <v>0.53898000000000001</v>
       </c>
       <c r="S45">
         <f t="shared" si="7"/>
-        <v>1.3120000000000023</v>
+        <v>1.3236000000000028</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -25288,11 +25288,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="C46">
-        <v>0.20765</v>
+        <v>0.20718</v>
       </c>
       <c r="D46">
         <f t="shared" si="4"/>
-        <v>0.59360000000000179</v>
+        <v>0.62840000000000229</v>
       </c>
       <c r="F46">
         <v>13.15</v>
@@ -25302,11 +25302,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="H46">
-        <v>0.44157999999999997</v>
+        <v>0.44142999999999999</v>
       </c>
       <c r="I46">
         <f t="shared" si="5"/>
-        <v>0.74600000000000266</v>
+        <v>0.72240000000000337</v>
       </c>
       <c r="K46">
         <v>13.15</v>
@@ -25316,11 +25316,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="M46">
-        <v>0.57393000000000005</v>
+        <v>0.57310000000000005</v>
       </c>
       <c r="N46">
         <f t="shared" si="6"/>
-        <v>1.0044000000000022</v>
+        <v>1.0200000000000022</v>
       </c>
       <c r="P46">
         <v>13.15</v>
@@ -25330,11 +25330,11 @@
         <v>1.3149999999999999</v>
       </c>
       <c r="R46">
-        <v>0.50595999999999997</v>
+        <v>0.50529000000000002</v>
       </c>
       <c r="S46">
         <f t="shared" si="7"/>
-        <v>1.4252000000000071</v>
+        <v>1.3476000000000048</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
@@ -25346,11 +25346,11 @@
         <v>1.34</v>
       </c>
       <c r="C47">
-        <v>0.19286</v>
+        <v>0.19419</v>
       </c>
       <c r="D47">
         <f t="shared" si="4"/>
-        <v>0.5915999999999968</v>
+        <v>0.51959999999999729</v>
       </c>
       <c r="F47">
         <v>13.4</v>
@@ -25360,11 +25360,11 @@
         <v>1.34</v>
       </c>
       <c r="H47">
-        <v>0.42349999999999999</v>
+        <v>0.42096</v>
       </c>
       <c r="I47">
         <f t="shared" si="5"/>
-        <v>0.72319999999999551</v>
+        <v>0.8187999999999952</v>
       </c>
       <c r="K47">
         <v>13.4</v>
@@ -25374,11 +25374,11 @@
         <v>1.34</v>
       </c>
       <c r="M47">
-        <v>0.54835999999999996</v>
+        <v>0.54652999999999996</v>
       </c>
       <c r="N47">
         <f t="shared" si="6"/>
-        <v>1.0227999999999982</v>
+        <v>1.062799999999998</v>
       </c>
       <c r="P47">
         <v>13.4</v>
@@ -25388,11 +25388,11 @@
         <v>1.34</v>
       </c>
       <c r="R47">
-        <v>0.47277999999999998</v>
+        <v>0.47222999999999998</v>
       </c>
       <c r="S47">
         <f t="shared" si="7"/>
-        <v>1.3271999999999924</v>
+        <v>1.3223999999999942</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
@@ -25404,11 +25404,11 @@
         <v>1.365</v>
       </c>
       <c r="C48">
-        <v>0.17979999999999999</v>
+        <v>0.18040999999999999</v>
       </c>
       <c r="D48">
         <f t="shared" si="4"/>
-        <v>0.52240000000000253</v>
+        <v>0.55120000000000258</v>
       </c>
       <c r="F48">
         <v>13.65</v>
@@ -25418,11 +25418,11 @@
         <v>1.365</v>
       </c>
       <c r="H48">
-        <v>0.40409</v>
+        <v>0.4042</v>
       </c>
       <c r="I48">
         <f t="shared" si="5"/>
-        <v>0.77640000000000209</v>
+        <v>0.67040000000000222</v>
       </c>
       <c r="K48">
         <v>13.65</v>
@@ -25432,11 +25432,11 @@
         <v>1.365</v>
       </c>
       <c r="M48">
-        <v>0.51900999999999997</v>
+        <v>0.51888000000000001</v>
       </c>
       <c r="N48">
         <f t="shared" si="6"/>
-        <v>1.1740000000000037</v>
+        <v>1.1060000000000021</v>
       </c>
       <c r="P48">
         <v>13.65</v>
@@ -25446,11 +25446,11 @@
         <v>1.365</v>
       </c>
       <c r="R48">
-        <v>0.43741999999999998</v>
+        <v>0.43640000000000001</v>
       </c>
       <c r="S48">
         <f t="shared" si="7"/>
-        <v>1.4144000000000052</v>
+        <v>1.433200000000004</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -25462,11 +25462,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="C49">
-        <v>0.16800000000000001</v>
+        <v>0.16939000000000001</v>
       </c>
       <c r="D49">
         <f t="shared" si="4"/>
-        <v>0.47199999999999659</v>
+        <v>0.44079999999999664</v>
       </c>
       <c r="F49">
         <v>13.9</v>
@@ -25476,11 +25476,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="H49">
-        <v>0.38466</v>
+        <v>0.38608999999999999</v>
       </c>
       <c r="I49">
         <f t="shared" si="5"/>
-        <v>0.77719999999999601</v>
+        <v>0.72439999999999671</v>
       </c>
       <c r="K49">
         <v>13.9</v>
@@ -25490,11 +25490,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="M49">
-        <v>0.48898999999999998</v>
+        <v>0.48998999999999998</v>
       </c>
       <c r="N49">
         <f t="shared" si="6"/>
-        <v>1.2007999999999932</v>
+        <v>1.1555999999999949</v>
       </c>
       <c r="P49">
         <v>13.9</v>
@@ -25504,11 +25504,11 @@
         <v>1.3900000000000001</v>
       </c>
       <c r="R49">
-        <v>0.40495999999999999</v>
+        <v>0.40183000000000002</v>
       </c>
       <c r="S49">
         <f t="shared" si="7"/>
-        <v>1.2983999999999927</v>
+        <v>1.3827999999999923</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
@@ -25520,11 +25520,11 @@
         <v>1.415</v>
       </c>
       <c r="C50">
-        <v>0.15620999999999999</v>
+        <v>0.15767</v>
       </c>
       <c r="D50">
         <f t="shared" si="4"/>
-        <v>0.47160000000000257</v>
+        <v>0.46880000000000199</v>
       </c>
       <c r="F50">
         <v>14.15</v>
@@ -25534,11 +25534,11 @@
         <v>1.415</v>
       </c>
       <c r="H50">
-        <v>0.36603000000000002</v>
+        <v>0.36737999999999998</v>
       </c>
       <c r="I50">
         <f t="shared" si="5"/>
-        <v>0.74520000000000186</v>
+        <v>0.74840000000000284</v>
       </c>
       <c r="K50">
         <v>14.15</v>
@@ -25548,11 +25548,11 @@
         <v>1.415</v>
       </c>
       <c r="M50">
-        <v>0.4577</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="N50">
         <f t="shared" si="6"/>
-        <v>1.2516000000000038</v>
+        <v>1.279600000000003</v>
       </c>
       <c r="P50">
         <v>14.15</v>
@@ -25562,11 +25562,11 @@
         <v>1.415</v>
       </c>
       <c r="R50">
-        <v>0.37079000000000001</v>
+        <v>0.36829000000000001</v>
       </c>
       <c r="S50">
         <f t="shared" si="7"/>
-        <v>1.366800000000004</v>
+        <v>1.3416000000000052</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
@@ -25578,11 +25578,11 @@
         <v>1.44</v>
       </c>
       <c r="C51">
-        <v>0.14399999999999999</v>
+        <v>0.14473</v>
       </c>
       <c r="D51">
         <f t="shared" si="4"/>
-        <v>0.48840000000000167</v>
+        <v>0.51760000000000217</v>
       </c>
       <c r="F51">
         <v>14.4</v>
@@ -25592,11 +25592,11 @@
         <v>1.44</v>
       </c>
       <c r="H51">
-        <v>0.34752</v>
+        <v>0.34892000000000001</v>
       </c>
       <c r="I51">
         <f t="shared" si="5"/>
-        <v>0.74040000000000372</v>
+        <v>0.73840000000000172</v>
       </c>
       <c r="K51">
         <v>14.4</v>
@@ -25606,11 +25606,11 @@
         <v>1.44</v>
       </c>
       <c r="M51">
-        <v>0.42682999999999999</v>
+        <v>0.42542999999999997</v>
       </c>
       <c r="N51">
         <f t="shared" si="6"/>
-        <v>1.2348000000000048</v>
+        <v>1.3028000000000064</v>
       </c>
       <c r="P51">
         <v>14.4</v>
@@ -25620,11 +25620,11 @@
         <v>1.44</v>
       </c>
       <c r="R51">
-        <v>0.33976000000000001</v>
+        <v>0.33706000000000003</v>
       </c>
       <c r="S51">
         <f t="shared" si="7"/>
-        <v>1.2412000000000045</v>
+        <v>1.2492000000000036</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
@@ -25636,11 +25636,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="C52">
-        <v>0.13511999999999999</v>
+        <v>0.13481000000000001</v>
       </c>
       <c r="D52">
         <f t="shared" si="4"/>
-        <v>0.35519999999999807</v>
+        <v>0.39679999999999727</v>
       </c>
       <c r="F52">
         <v>14.65</v>
@@ -25650,11 +25650,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="H52">
-        <v>0.33123999999999998</v>
+        <v>0.33058999999999999</v>
       </c>
       <c r="I52">
         <f t="shared" si="5"/>
-        <v>0.65119999999999723</v>
+        <v>0.73319999999999663</v>
       </c>
       <c r="K52">
         <v>14.65</v>
@@ -25664,11 +25664,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="M52">
-        <v>0.39361000000000002</v>
+        <v>0.39362000000000003</v>
       </c>
       <c r="N52">
         <f t="shared" si="6"/>
-        <v>1.3287999999999918</v>
+        <v>1.2723999999999911</v>
       </c>
       <c r="P52">
         <v>14.65</v>
@@ -25678,11 +25678,11 @@
         <v>1.4650000000000001</v>
       </c>
       <c r="R52">
-        <v>0.30959999999999999</v>
+        <v>0.30797000000000002</v>
       </c>
       <c r="S52">
         <f t="shared" si="7"/>
-        <v>1.2063999999999944</v>
+        <v>1.163599999999994</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
@@ -25694,11 +25694,11 @@
         <v>1.49</v>
       </c>
       <c r="C53">
-        <v>0.12418999999999999</v>
+        <v>0.12586</v>
       </c>
       <c r="D53">
         <f t="shared" si="4"/>
-        <v>0.43720000000000137</v>
+        <v>0.35800000000000182</v>
       </c>
       <c r="F53">
         <v>14.9</v>
@@ -25708,11 +25708,11 @@
         <v>1.49</v>
       </c>
       <c r="H53">
-        <v>0.31283</v>
+        <v>0.31167</v>
       </c>
       <c r="I53">
         <f t="shared" si="5"/>
-        <v>0.73640000000000194</v>
+        <v>0.75680000000000236</v>
       </c>
       <c r="K53">
         <v>14.9</v>
@@ -25722,11 +25722,11 @@
         <v>1.49</v>
       </c>
       <c r="M53">
-        <v>0.36325000000000002</v>
+        <v>0.36381999999999998</v>
       </c>
       <c r="N53">
         <f t="shared" si="6"/>
-        <v>1.2144000000000041</v>
+        <v>1.1920000000000062</v>
       </c>
       <c r="P53">
         <v>14.9</v>
@@ -25736,11 +25736,11 @@
         <v>1.49</v>
       </c>
       <c r="R53">
-        <v>0.2792</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="S53">
         <f t="shared" si="7"/>
-        <v>1.2160000000000035</v>
+        <v>1.1988000000000041</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
@@ -25752,11 +25752,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="C54">
-        <v>0.11550000000000001</v>
+        <v>0.11734</v>
       </c>
       <c r="D54">
         <f t="shared" si="4"/>
-        <v>0.34759999999999774</v>
+        <v>0.34079999999999816</v>
       </c>
       <c r="F54">
         <v>15.15</v>
@@ -25766,11 +25766,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="H54">
-        <v>0.29737999999999998</v>
+        <v>0.29349999999999998</v>
       </c>
       <c r="I54">
         <f t="shared" si="5"/>
-        <v>0.61799999999999744</v>
+        <v>0.72679999999999689</v>
       </c>
       <c r="K54">
         <v>15.15</v>
@@ -25780,11 +25780,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="M54">
-        <v>0.33128999999999997</v>
+        <v>0.33061000000000001</v>
       </c>
       <c r="N54">
         <f t="shared" si="6"/>
-        <v>1.2783999999999949</v>
+        <v>1.3283999999999914</v>
       </c>
       <c r="P54">
         <v>15.15</v>
@@ -25794,11 +25794,11 @@
         <v>1.5150000000000001</v>
       </c>
       <c r="R54">
-        <v>0.25087999999999999</v>
+        <v>0.25008000000000002</v>
       </c>
       <c r="S54">
         <f t="shared" si="7"/>
-        <v>1.1327999999999945</v>
+        <v>1.116799999999994</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
@@ -25810,11 +25810,11 @@
         <v>1.54</v>
       </c>
       <c r="C55">
-        <v>0.10788</v>
+        <v>0.10847</v>
       </c>
       <c r="D55">
         <f t="shared" si="4"/>
-        <v>0.30480000000000118</v>
+        <v>0.35480000000000139</v>
       </c>
       <c r="F55">
         <v>15.4</v>
@@ -25824,11 +25824,11 @@
         <v>1.54</v>
       </c>
       <c r="H55">
-        <v>0.28165000000000001</v>
+        <v>0.27843000000000001</v>
       </c>
       <c r="I55">
         <f t="shared" si="5"/>
-        <v>0.62920000000000087</v>
+        <v>0.602800000000001</v>
       </c>
       <c r="K55">
         <v>15.4</v>
@@ -25838,11 +25838,11 @@
         <v>1.54</v>
       </c>
       <c r="M55">
-        <v>0.29965999999999998</v>
+        <v>0.29959999999999998</v>
       </c>
       <c r="N55">
         <f t="shared" si="6"/>
-        <v>1.2652000000000041</v>
+        <v>1.2404000000000059</v>
       </c>
       <c r="P55">
         <v>15.4</v>
@@ -25852,11 +25852,11 @@
         <v>1.54</v>
       </c>
       <c r="R55">
-        <v>0.22056000000000001</v>
+        <v>0.22262999999999999</v>
       </c>
       <c r="S55">
         <f t="shared" si="7"/>
-        <v>1.2128000000000037</v>
+        <v>1.0980000000000052</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
@@ -25868,11 +25868,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="C56">
-        <v>9.9580000000000002E-2</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="D56">
         <f t="shared" si="4"/>
-        <v>0.33200000000000124</v>
+        <v>0.36680000000000118</v>
       </c>
       <c r="F56">
         <v>15.65</v>
@@ -25882,11 +25882,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="H56">
-        <v>0.26408999999999999</v>
+        <v>0.26251000000000002</v>
       </c>
       <c r="I56">
         <f t="shared" si="5"/>
-        <v>0.70240000000000324</v>
+        <v>0.63680000000000181</v>
       </c>
       <c r="K56">
         <v>15.65</v>
@@ -25896,11 +25896,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="M56">
-        <v>0.27123000000000003</v>
+        <v>0.27262999999999998</v>
       </c>
       <c r="N56">
         <f t="shared" si="6"/>
-        <v>1.1372000000000022</v>
+        <v>1.0788000000000035</v>
       </c>
       <c r="P56">
         <v>15.65</v>
@@ -25910,11 +25910,11 @@
         <v>1.5649999999999999</v>
       </c>
       <c r="R56">
-        <v>0.19378999999999999</v>
+        <v>0.19841</v>
       </c>
       <c r="S56">
         <f t="shared" si="7"/>
-        <v>1.0708000000000044</v>
+        <v>0.9688000000000031</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
@@ -25926,11 +25926,11 @@
         <v>1.59</v>
       </c>
       <c r="C57">
-        <v>9.0980000000000005E-2</v>
+        <v>9.2149999999999996E-2</v>
       </c>
       <c r="D57">
         <f t="shared" si="4"/>
-        <v>0.34399999999999803</v>
+        <v>0.28599999999999864</v>
       </c>
       <c r="F57">
         <v>15.9</v>
@@ -25940,11 +25940,11 @@
         <v>1.59</v>
       </c>
       <c r="H57">
-        <v>0.24823000000000001</v>
+        <v>0.24737999999999999</v>
       </c>
       <c r="I57">
         <f t="shared" si="5"/>
-        <v>0.63439999999999608</v>
+        <v>0.60519999999999807</v>
       </c>
       <c r="K57">
         <v>15.9</v>
@@ -25954,11 +25954,11 @@
         <v>1.59</v>
       </c>
       <c r="M57">
-        <v>0.2417</v>
+        <v>0.24303</v>
       </c>
       <c r="N57">
         <f t="shared" si="6"/>
-        <v>1.1811999999999949</v>
+        <v>1.1839999999999933</v>
       </c>
       <c r="P57">
         <v>15.9</v>
@@ -25968,11 +25968,11 @@
         <v>1.59</v>
       </c>
       <c r="R57">
-        <v>0.16903000000000001</v>
+        <v>0.17146</v>
       </c>
       <c r="S57">
         <f t="shared" si="7"/>
-        <v>0.99039999999999373</v>
+        <v>1.0779999999999943</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
@@ -25984,11 +25984,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="C58">
-        <v>8.4669999999999995E-2</v>
+        <v>8.4699999999999998E-2</v>
       </c>
       <c r="D58">
         <f t="shared" si="4"/>
-        <v>0.25240000000000357</v>
+        <v>0.29800000000000365</v>
       </c>
       <c r="F58">
         <v>16.149999999999999</v>
@@ -25998,11 +25998,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="H58">
-        <v>0.23266000000000001</v>
+        <v>0.2301</v>
       </c>
       <c r="I58">
         <f t="shared" si="5"/>
-        <v>0.62280000000000779</v>
+        <v>0.69120000000000814</v>
       </c>
       <c r="K58">
         <v>16.149999999999999</v>
@@ -26012,11 +26012,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="M58">
-        <v>0.21489</v>
+        <v>0.21240000000000001</v>
       </c>
       <c r="N58">
         <f t="shared" si="6"/>
-        <v>1.0724000000000133</v>
+        <v>1.2252000000000149</v>
       </c>
       <c r="P58">
         <v>16.149999999999999</v>
@@ -26026,11 +26026,11 @@
         <v>1.6149999999999998</v>
       </c>
       <c r="R58">
-        <v>0.14773</v>
+        <v>0.14754</v>
       </c>
       <c r="S58">
         <f t="shared" si="7"/>
-        <v>0.85200000000001108</v>
+        <v>0.95680000000001175</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
@@ -26042,11 +26042,11 @@
         <v>1.64</v>
       </c>
       <c r="C59">
-        <v>7.6259999999999994E-2</v>
+        <v>7.5319999999999998E-2</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.33639999999999826</v>
+        <v>0.37519999999999798</v>
       </c>
       <c r="F59">
         <v>16.399999999999999</v>
@@ -26056,11 +26056,11 @@
         <v>1.64</v>
       </c>
       <c r="H59">
-        <v>0.21826999999999999</v>
+        <v>0.21592</v>
       </c>
       <c r="I59">
         <f t="shared" si="5"/>
-        <v>0.57559999999999745</v>
+        <v>0.56719999999999693</v>
       </c>
       <c r="K59">
         <v>16.399999999999999</v>
@@ -26070,11 +26070,11 @@
         <v>1.64</v>
       </c>
       <c r="M59">
-        <v>0.18789</v>
+        <v>0.18542</v>
       </c>
       <c r="N59">
         <f t="shared" si="6"/>
-        <v>1.0799999999999941</v>
+        <v>1.0791999999999944</v>
       </c>
       <c r="P59">
         <v>16.399999999999999</v>
@@ -26084,11 +26084,11 @@
         <v>1.64</v>
       </c>
       <c r="R59">
-        <v>0.12945999999999999</v>
+        <v>0.13027</v>
       </c>
       <c r="S59">
         <f t="shared" si="7"/>
-        <v>0.73079999999999645</v>
+        <v>0.69079999999999664</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
@@ -26100,11 +26100,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="C60">
-        <v>6.7750000000000005E-2</v>
+        <v>6.9019999999999998E-2</v>
       </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0.34040000000000081</v>
+        <v>0.25200000000000089</v>
       </c>
       <c r="F60">
         <v>16.649999999999999</v>
@@ -26114,11 +26114,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="H60">
-        <v>0.20397000000000001</v>
+        <v>0.20233999999999999</v>
       </c>
       <c r="I60">
         <f t="shared" si="5"/>
-        <v>0.57200000000000117</v>
+        <v>0.54320000000000224</v>
       </c>
       <c r="K60">
         <v>16.649999999999999</v>
@@ -26128,11 +26128,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="M60">
-        <v>0.16053000000000001</v>
+        <v>0.16224</v>
       </c>
       <c r="N60">
         <f t="shared" si="6"/>
-        <v>1.0944000000000038</v>
+        <v>0.92720000000000358</v>
       </c>
       <c r="P60">
         <v>16.649999999999999</v>
@@ -26142,11 +26142,11 @@
         <v>1.6649999999999998</v>
       </c>
       <c r="R60">
-        <v>0.11123</v>
+        <v>0.11396000000000001</v>
       </c>
       <c r="S60">
         <f t="shared" si="7"/>
-        <v>0.7292000000000024</v>
+        <v>0.65240000000000198</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
@@ -26158,11 +26158,11 @@
         <v>1.69</v>
       </c>
       <c r="C61">
-        <v>6.021E-2</v>
+        <v>6.2330000000000003E-2</v>
       </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0.30159999999999859</v>
+        <v>0.26759999999999834</v>
       </c>
       <c r="F61">
         <v>16.899999999999999</v>
@@ -26172,11 +26172,11 @@
         <v>1.69</v>
       </c>
       <c r="H61">
-        <v>0.19189999999999999</v>
+        <v>0.18898000000000001</v>
       </c>
       <c r="I61">
         <f t="shared" si="5"/>
-        <v>0.48279999999999845</v>
+        <v>0.53439999999999643</v>
       </c>
       <c r="K61">
         <v>16.899999999999999</v>
@@ -26186,11 +26186,11 @@
         <v>1.69</v>
       </c>
       <c r="M61">
-        <v>0.13925999999999999</v>
+        <v>0.14197000000000001</v>
       </c>
       <c r="N61">
         <f t="shared" si="6"/>
-        <v>0.85079999999999589</v>
+        <v>0.81079999999999497</v>
       </c>
       <c r="P61">
         <v>16.899999999999999</v>
@@ -26200,11 +26200,11 @@
         <v>1.69</v>
       </c>
       <c r="R61">
-        <v>9.2450000000000004E-2</v>
+        <v>9.7379999999999994E-2</v>
       </c>
       <c r="S61">
         <f t="shared" si="7"/>
-        <v>0.75119999999999565</v>
+        <v>0.6631999999999969</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
@@ -26216,11 +26216,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="C62">
-        <v>5.4120000000000001E-2</v>
+        <v>5.3839999999999999E-2</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0.24360000000000079</v>
+        <v>0.3396000000000014</v>
       </c>
       <c r="F62">
         <v>17.149999999999999</v>
@@ -26230,11 +26230,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="H62">
-        <v>0.17660000000000001</v>
+        <v>0.1759</v>
       </c>
       <c r="I62">
         <f t="shared" si="5"/>
-        <v>0.61200000000000143</v>
+        <v>0.52320000000000222</v>
       </c>
       <c r="K62">
         <v>17.149999999999999</v>
@@ -26244,11 +26244,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="M62">
-        <v>0.12286</v>
+        <v>0.12095</v>
       </c>
       <c r="N62">
         <f t="shared" si="6"/>
-        <v>0.65600000000000225</v>
+        <v>0.84080000000000343</v>
       </c>
       <c r="P62">
         <v>17.149999999999999</v>
@@ -26258,11 +26258,11 @@
         <v>1.7149999999999999</v>
       </c>
       <c r="R62">
-        <v>7.5429999999999997E-2</v>
+        <v>8.0549999999999997E-2</v>
       </c>
       <c r="S62">
         <f t="shared" si="7"/>
-        <v>0.68080000000000274</v>
+        <v>0.67320000000000235</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
@@ -26274,11 +26274,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="C63">
-        <v>4.6339999999999999E-2</v>
+        <v>4.6780000000000002E-2</v>
       </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0.3112000000000012</v>
+        <v>0.28240000000000087</v>
       </c>
       <c r="F63">
         <v>17.399999999999999</v>
@@ -26288,11 +26288,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="H63">
-        <v>0.16406999999999999</v>
+        <v>0.16545000000000001</v>
       </c>
       <c r="I63">
         <f t="shared" si="5"/>
-        <v>0.50120000000000231</v>
+        <v>0.41800000000000098</v>
       </c>
       <c r="K63">
         <v>17.399999999999999</v>
@@ -26302,11 +26302,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="M63">
-        <v>0.10360999999999999</v>
+        <v>0.10358000000000001</v>
       </c>
       <c r="N63">
         <f t="shared" si="6"/>
-        <v>0.7700000000000029</v>
+        <v>0.6948000000000023</v>
       </c>
       <c r="P63">
         <v>17.399999999999999</v>
@@ -26316,11 +26316,11 @@
         <v>1.7399999999999998</v>
       </c>
       <c r="R63">
-        <v>6.6129999999999994E-2</v>
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="S63">
         <f t="shared" si="7"/>
-        <v>0.37200000000000144</v>
+        <v>0.50600000000000156</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
@@ -26332,11 +26332,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="C64">
-        <v>3.9129999999999998E-2</v>
+        <v>4.0989999999999999E-2</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.28839999999999849</v>
+        <v>0.23159999999999892</v>
       </c>
       <c r="F64">
         <v>17.649999999999999</v>
@@ -26346,11 +26346,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="H64">
-        <v>0.15256</v>
+        <v>0.15342</v>
       </c>
       <c r="I64">
         <f t="shared" si="5"/>
-        <v>0.46039999999999726</v>
+        <v>0.48119999999999796</v>
       </c>
       <c r="K64">
         <v>17.649999999999999</v>
@@ -26360,11 +26360,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="M64">
-        <v>8.9620000000000005E-2</v>
+        <v>8.8520000000000001E-2</v>
       </c>
       <c r="N64">
         <f t="shared" si="6"/>
-        <v>0.55959999999999654</v>
+        <v>0.60239999999999694</v>
       </c>
       <c r="P64">
         <v>17.649999999999999</v>
@@ -26374,11 +26374,11 @@
         <v>1.7649999999999999</v>
       </c>
       <c r="R64">
-        <v>5.6669999999999998E-2</v>
+        <v>5.8250000000000003E-2</v>
       </c>
       <c r="S64">
         <f t="shared" si="7"/>
-        <v>0.37839999999999785</v>
+        <v>0.3859999999999979</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
@@ -26390,11 +26390,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="C65">
-        <v>3.3599999999999998E-2</v>
+        <v>3.388E-2</v>
       </c>
       <c r="D65">
         <f t="shared" si="4"/>
-        <v>0.22120000000000078</v>
+        <v>0.28440000000000093</v>
       </c>
       <c r="F65">
         <v>17.899999999999999</v>
@@ -26404,11 +26404,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="H65">
-        <v>0.14388999999999999</v>
+        <v>0.14310999999999999</v>
       </c>
       <c r="I65">
         <f t="shared" si="5"/>
-        <v>0.34680000000000166</v>
+        <v>0.41240000000000199</v>
       </c>
       <c r="K65">
         <v>17.899999999999999</v>
@@ -26418,11 +26418,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="M65">
-        <v>7.5569999999999998E-2</v>
+        <v>7.578E-2</v>
       </c>
       <c r="N65">
         <f t="shared" si="6"/>
-        <v>0.56200000000000228</v>
+        <v>0.50960000000000183</v>
       </c>
       <c r="P65">
         <v>17.899999999999999</v>
@@ -26432,11 +26432,11 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="R65">
-        <v>4.8849999999999998E-2</v>
+        <v>4.9259999999999998E-2</v>
       </c>
       <c r="S65">
         <f t="shared" si="7"/>
-        <v>0.31280000000000113</v>
+        <v>0.35960000000000147</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
@@ -26448,11 +26448,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="C66">
-        <v>2.6270000000000002E-2</v>
+        <v>2.8080000000000001E-2</v>
       </c>
       <c r="D66">
         <f t="shared" si="4"/>
-        <v>0.2931999999999983</v>
+        <v>0.23199999999999874</v>
       </c>
       <c r="F66">
         <v>18.149999999999999</v>
@@ -26462,11 +26462,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="H66">
-        <v>0.13425999999999999</v>
+        <v>0.13439000000000001</v>
       </c>
       <c r="I66">
         <f t="shared" si="5"/>
-        <v>0.38519999999999793</v>
+        <v>0.34879999999999728</v>
       </c>
       <c r="K66">
         <v>18.149999999999999</v>
@@ -26476,11 +26476,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="M66">
-        <v>6.3140000000000002E-2</v>
+        <v>6.0229999999999999E-2</v>
       </c>
       <c r="N66">
         <f t="shared" si="6"/>
-        <v>0.4971999999999972</v>
+        <v>0.62199999999999678</v>
       </c>
       <c r="P66">
         <v>18.149999999999999</v>
@@ -26490,11 +26490,11 @@
         <v>1.8149999999999999</v>
       </c>
       <c r="R66">
-        <v>4.4089999999999997E-2</v>
+        <v>4.3409999999999997E-2</v>
       </c>
       <c r="S66">
         <f t="shared" si="7"/>
-        <v>0.19039999999999899</v>
+        <v>0.23399999999999879</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
@@ -26506,11 +26506,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="C67">
-        <v>2.2790000000000001E-2</v>
+        <v>2.4080000000000001E-2</v>
       </c>
       <c r="D67">
         <f t="shared" si="4"/>
-        <v>0.13920000000000052</v>
+        <v>0.16000000000000056</v>
       </c>
       <c r="F67">
         <v>18.399999999999999</v>
@@ -26520,11 +26520,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="H67">
-        <v>0.12446</v>
+        <v>0.12726000000000001</v>
       </c>
       <c r="I67">
         <f t="shared" si="5"/>
-        <v>0.39200000000000096</v>
+        <v>0.2852000000000009</v>
       </c>
       <c r="K67">
         <v>18.399999999999999</v>
@@ -26534,11 +26534,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="M67">
-        <v>5.3249999999999999E-2</v>
+        <v>5.1249999999999997E-2</v>
       </c>
       <c r="N67">
         <f t="shared" si="6"/>
-        <v>0.39560000000000151</v>
+        <v>0.35920000000000135</v>
       </c>
       <c r="P67">
         <v>18.399999999999999</v>
@@ -26548,11 +26548,11 @@
         <v>1.8399999999999999</v>
       </c>
       <c r="R67">
-        <v>3.576E-2</v>
+        <v>3.7870000000000001E-2</v>
       </c>
       <c r="S67">
         <f t="shared" si="7"/>
-        <v>0.33320000000000105</v>
+        <v>0.22160000000000063</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
@@ -26564,11 +26564,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="C68">
-        <v>1.753E-2</v>
+        <v>1.7909999999999999E-2</v>
       </c>
       <c r="D68">
         <f t="shared" si="4"/>
-        <v>0.21040000000000078</v>
+        <v>0.24680000000000096</v>
       </c>
       <c r="F68">
         <v>18.649999999999999</v>
@@ -26578,11 +26578,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="H68">
-        <v>0.11806</v>
+        <v>0.11787</v>
       </c>
       <c r="I68">
         <f t="shared" si="5"/>
-        <v>0.256000000000001</v>
+        <v>0.37560000000000171</v>
       </c>
       <c r="K68">
         <v>18.649999999999999</v>
@@ -26592,11 +26592,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="M68">
-        <v>4.4979999999999999E-2</v>
+        <v>4.5420000000000002E-2</v>
       </c>
       <c r="N68">
         <f t="shared" si="6"/>
-        <v>0.33080000000000115</v>
+        <v>0.23320000000000063</v>
       </c>
       <c r="P68">
         <v>18.649999999999999</v>
@@ -26606,11 +26606,11 @@
         <v>1.8649999999999998</v>
       </c>
       <c r="R68">
-        <v>3.0620000000000001E-2</v>
+        <v>3.2669999999999998E-2</v>
       </c>
       <c r="S68">
         <f t="shared" si="7"/>
-        <v>0.20560000000000067</v>
+        <v>0.20800000000000088</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
@@ -26622,11 +26622,11 @@
         <v>1.89</v>
       </c>
       <c r="C69">
-        <v>1.3129999999999999E-2</v>
+        <v>1.325E-2</v>
       </c>
       <c r="D69">
         <f t="shared" si="4"/>
-        <v>0.1759999999999991</v>
+        <v>0.18639999999999898</v>
       </c>
       <c r="F69">
         <v>18.899999999999999</v>
@@ -26636,11 +26636,11 @@
         <v>1.89</v>
       </c>
       <c r="H69">
-        <v>0.10724</v>
+        <v>0.10957</v>
       </c>
       <c r="I69">
         <f t="shared" si="5"/>
-        <v>0.43279999999999752</v>
+        <v>0.3319999999999983</v>
       </c>
       <c r="K69">
         <v>18.899999999999999</v>
@@ -26650,11 +26650,11 @@
         <v>1.89</v>
       </c>
       <c r="M69">
-        <v>3.8530000000000002E-2</v>
+        <v>3.669E-2</v>
       </c>
       <c r="N69">
         <f t="shared" si="6"/>
-        <v>0.25799999999999851</v>
+        <v>0.34919999999999818</v>
       </c>
       <c r="P69">
         <v>18.899999999999999</v>
@@ -26664,11 +26664,11 @@
         <v>1.89</v>
       </c>
       <c r="R69">
-        <v>2.5239999999999999E-2</v>
+        <v>2.7179999999999999E-2</v>
       </c>
       <c r="S69">
         <f t="shared" si="7"/>
-        <v>0.21519999999999898</v>
+        <v>0.21959999999999877</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
@@ -26680,11 +26680,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="C70">
-        <v>8.6700000000000006E-3</v>
+        <v>7.4900000000000001E-3</v>
       </c>
       <c r="D70">
         <f t="shared" si="4"/>
-        <v>0.17840000000000059</v>
+        <v>0.2304000000000008</v>
       </c>
       <c r="F70">
         <v>19.149999999999999</v>
@@ -26694,11 +26694,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="H70">
-        <v>9.9239999999999995E-2</v>
+        <v>0.10285</v>
       </c>
       <c r="I70">
         <f t="shared" si="5"/>
-        <v>0.32000000000000139</v>
+        <v>0.26880000000000109</v>
       </c>
       <c r="K70">
         <v>19.149999999999999</v>
@@ -26708,11 +26708,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="M70">
-        <v>3.005E-2</v>
+        <v>3.2779999999999997E-2</v>
       </c>
       <c r="N70">
         <f t="shared" si="6"/>
-        <v>0.33920000000000128</v>
+        <v>0.15640000000000071</v>
       </c>
       <c r="P70">
         <v>19.149999999999999</v>
@@ -26722,11 +26722,11 @@
         <v>1.9149999999999998</v>
       </c>
       <c r="R70">
-        <v>1.9650000000000001E-2</v>
+        <v>2.0289999999999999E-2</v>
       </c>
       <c r="S70">
         <f t="shared" si="7"/>
-        <v>0.22360000000000071</v>
+        <v>0.27560000000000101</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
@@ -26738,11 +26738,11 @@
         <v>1.94</v>
       </c>
       <c r="C71">
-        <v>5.2399999999999999E-3</v>
+        <v>6.6499999999999997E-3</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D78" si="12">(C70-C71)/(B71-B70)</f>
-        <v>0.13719999999999929</v>
+        <v>3.3599999999999838E-2</v>
       </c>
       <c r="F71">
         <v>19.399999999999999</v>
@@ -26752,11 +26752,11 @@
         <v>1.94</v>
       </c>
       <c r="H71">
-        <v>9.3410000000000007E-2</v>
+        <v>9.5219999999999999E-2</v>
       </c>
       <c r="I71">
         <f t="shared" ref="I71:I94" si="13">(H70-H71)/(G71-G70)</f>
-        <v>0.23319999999999827</v>
+        <v>0.30519999999999831</v>
       </c>
       <c r="K71">
         <v>19.399999999999999</v>
@@ -26766,11 +26766,11 @@
         <v>1.94</v>
       </c>
       <c r="M71">
-        <v>2.529E-2</v>
+        <v>2.5559999999999999E-2</v>
       </c>
       <c r="N71">
         <f t="shared" ref="N71:N94" si="14">(M70-M71)/(L71-L70)</f>
-        <v>0.19039999999999899</v>
+        <v>0.28879999999999834</v>
       </c>
       <c r="P71">
         <v>19.399999999999999</v>
@@ -26780,11 +26780,11 @@
         <v>1.94</v>
       </c>
       <c r="R71">
-        <v>1.174E-2</v>
+        <v>1.5089999999999999E-2</v>
       </c>
       <c r="S71">
         <f t="shared" ref="S71:S94" si="15">(R70-R71)/(Q71-Q70)</f>
-        <v>0.31639999999999835</v>
+        <v>0.20799999999999888</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
@@ -26796,11 +26796,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="C72">
-        <v>4.2100000000000002E-3</v>
+        <v>5.6100000000000004E-3</v>
       </c>
       <c r="D72">
         <f t="shared" si="12"/>
-        <v>4.1200000000000132E-2</v>
+        <v>4.1600000000000116E-2</v>
       </c>
       <c r="F72">
         <v>19.649999999999999</v>
@@ -26810,11 +26810,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="H72">
-        <v>8.5739999999999997E-2</v>
+        <v>8.7620000000000003E-2</v>
       </c>
       <c r="I72">
         <f t="shared" si="13"/>
-        <v>0.30680000000000152</v>
+        <v>0.30400000000000088</v>
       </c>
       <c r="K72">
         <v>19.649999999999999</v>
@@ -26824,11 +26824,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="M72">
-        <v>2.078E-2</v>
+        <v>2.1749999999999999E-2</v>
       </c>
       <c r="N72">
         <f t="shared" si="14"/>
-        <v>0.18040000000000064</v>
+        <v>0.15240000000000059</v>
       </c>
       <c r="P72">
         <v>19.649999999999999</v>
@@ -26838,11 +26838,11 @@
         <v>1.9649999999999999</v>
       </c>
       <c r="R72">
-        <v>8.0300000000000007E-3</v>
+        <v>8.7399999999999995E-3</v>
       </c>
       <c r="S72">
         <f t="shared" si="15"/>
-        <v>0.1484000000000005</v>
+        <v>0.25400000000000089</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
@@ -26854,11 +26854,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="C73">
-        <v>2.8700000000000002E-3</v>
+        <v>2.96E-3</v>
       </c>
       <c r="D73">
         <f t="shared" si="12"/>
-        <v>5.3600000000000189E-2</v>
+        <v>0.1060000000000004</v>
       </c>
       <c r="F73">
         <v>19.899999999999999</v>
@@ -26868,11 +26868,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="H73">
-        <v>7.8869999999999996E-2</v>
+        <v>8.0909999999999996E-2</v>
       </c>
       <c r="I73">
         <f t="shared" si="13"/>
-        <v>0.27480000000000104</v>
+        <v>0.26840000000000125</v>
       </c>
       <c r="K73">
         <v>19.899999999999999</v>
@@ -26882,11 +26882,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="M73">
-        <v>1.4749999999999999E-2</v>
+        <v>1.6449999999999999E-2</v>
       </c>
       <c r="N73">
         <f t="shared" si="14"/>
-        <v>0.24120000000000089</v>
+        <v>0.21200000000000072</v>
       </c>
       <c r="P73">
         <v>19.899999999999999</v>
@@ -26896,11 +26896,11 @@
         <v>1.9899999999999998</v>
       </c>
       <c r="R73">
-        <v>4.1399999999999996E-3</v>
+        <v>5.2300000000000003E-3</v>
       </c>
       <c r="S73">
         <f t="shared" si="15"/>
-        <v>0.1556000000000006</v>
+        <v>0.14040000000000047</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
@@ -26912,11 +26912,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="C74">
-        <v>1.6800000000000001E-3</v>
+        <v>2.2799999999999999E-3</v>
       </c>
       <c r="D74">
         <f t="shared" si="12"/>
-        <v>4.760000000000017E-2</v>
+        <v>2.7200000000000099E-2</v>
       </c>
       <c r="F74">
         <v>20.149999999999999</v>
@@ -26926,11 +26926,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="H74">
-        <v>7.0069999999999993E-2</v>
+        <v>7.2620000000000004E-2</v>
       </c>
       <c r="I74">
         <f t="shared" si="13"/>
-        <v>0.35200000000000137</v>
+        <v>0.33160000000000084</v>
       </c>
       <c r="K74">
         <v>20.149999999999999</v>
@@ -26940,11 +26940,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="M74">
-        <v>9.8700000000000003E-3</v>
+        <v>1.2460000000000001E-2</v>
       </c>
       <c r="N74">
         <f t="shared" si="14"/>
-        <v>0.19520000000000065</v>
+        <v>0.15960000000000052</v>
       </c>
       <c r="P74">
         <v>20.149999999999999</v>
@@ -26954,11 +26954,11 @@
         <v>2.0149999999999997</v>
       </c>
       <c r="R74">
-        <v>2.2100000000000002E-3</v>
+        <v>2.0699999999999998E-3</v>
       </c>
       <c r="S74">
         <f t="shared" si="15"/>
-        <v>7.7200000000000255E-2</v>
+        <v>0.12640000000000046</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
@@ -26970,11 +26970,11 @@
         <v>2.04</v>
       </c>
       <c r="C75">
-        <v>1.2800000000000001E-3</v>
+        <v>1.6800000000000001E-3</v>
       </c>
       <c r="D75">
         <f t="shared" si="12"/>
-        <v>1.5999999999999771E-2</v>
+        <v>2.3999999999999654E-2</v>
       </c>
       <c r="F75">
         <v>20.399999999999999</v>
@@ -26984,11 +26984,11 @@
         <v>2.04</v>
       </c>
       <c r="H75">
-        <v>6.1240000000000003E-2</v>
+        <v>6.5320000000000003E-2</v>
       </c>
       <c r="I75">
         <f t="shared" si="13"/>
-        <v>0.35319999999999463</v>
+        <v>0.29199999999999587</v>
       </c>
       <c r="K75">
         <v>20.399999999999999</v>
@@ -26998,11 +26998,11 @@
         <v>2.04</v>
       </c>
       <c r="M75">
-        <v>5.5599999999999998E-3</v>
+        <v>6.8300000000000001E-3</v>
       </c>
       <c r="N75">
         <f t="shared" si="14"/>
-        <v>0.17239999999999756</v>
+        <v>0.22519999999999682</v>
       </c>
       <c r="P75">
         <v>20.399999999999999</v>
@@ -27012,11 +27012,11 @@
         <v>2.04</v>
       </c>
       <c r="R75">
-        <v>5.4000000000000001E-4</v>
+        <v>1.0200000000000001E-3</v>
       </c>
       <c r="S75">
         <f t="shared" si="15"/>
-        <v>6.6799999999999055E-2</v>
+        <v>4.1999999999999392E-2</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
@@ -27028,11 +27028,11 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="C76">
-        <v>6.4000000000000005E-4</v>
+        <v>6.6E-4</v>
       </c>
       <c r="D76">
         <f t="shared" si="12"/>
-        <v>2.5600000000000091E-2</v>
+        <v>4.0800000000000149E-2</v>
       </c>
       <c r="F76">
         <v>20.65</v>
@@ -27042,11 +27042,11 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="H76">
-        <v>5.1950000000000003E-2</v>
+        <v>5.6750000000000002E-2</v>
       </c>
       <c r="I76">
         <f t="shared" si="13"/>
-        <v>0.37160000000000132</v>
+        <v>0.34280000000000127</v>
       </c>
       <c r="K76">
         <v>20.65</v>
@@ -27056,11 +27056,11 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="M76">
-        <v>3.9399999999999999E-3</v>
+        <v>2.8600000000000001E-3</v>
       </c>
       <c r="N76">
         <f t="shared" si="14"/>
-        <v>6.4800000000000232E-2</v>
+        <v>0.15880000000000055</v>
       </c>
       <c r="P76">
         <v>20.65</v>
@@ -27070,11 +27070,11 @@
         <v>2.0649999999999999</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>9.7000000000000005E-4</v>
       </c>
       <c r="S76">
         <f t="shared" si="15"/>
-        <v>2.1600000000000077E-2</v>
+        <v>2.0000000000000078E-3</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
@@ -27090,7 +27090,7 @@
       </c>
       <c r="D77">
         <f t="shared" si="12"/>
-        <v>2.5600000000000091E-2</v>
+        <v>2.6400000000000094E-2</v>
       </c>
       <c r="F77">
         <v>20.9</v>
@@ -27100,11 +27100,11 @@
         <v>2.09</v>
       </c>
       <c r="H77">
-        <v>4.6260000000000003E-2</v>
+        <v>4.8410000000000002E-2</v>
       </c>
       <c r="I77">
         <f t="shared" si="13"/>
-        <v>0.22760000000000083</v>
+        <v>0.33360000000000117</v>
       </c>
       <c r="K77">
         <v>20.9</v>
@@ -27114,11 +27114,11 @@
         <v>2.09</v>
       </c>
       <c r="M77">
-        <v>2.7699999999999999E-3</v>
+        <v>2.2699999999999999E-3</v>
       </c>
       <c r="N77">
         <f t="shared" si="14"/>
-        <v>4.6800000000000168E-2</v>
+        <v>2.3600000000000093E-2</v>
       </c>
       <c r="P77">
         <v>20.9</v>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S77">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3.880000000000014E-2</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
@@ -27158,11 +27158,11 @@
         <v>2.1149999999999998</v>
       </c>
       <c r="H78">
-        <v>4.0050000000000002E-2</v>
+        <v>4.086E-2</v>
       </c>
       <c r="I78">
         <f t="shared" si="13"/>
-        <v>0.2484000000000009</v>
+        <v>0.3020000000000011</v>
       </c>
       <c r="K78">
         <v>21.15</v>
@@ -27172,11 +27172,11 @@
         <v>2.1149999999999998</v>
       </c>
       <c r="M78">
-        <v>1.4599999999999999E-3</v>
+        <v>4.4999999999999999E-4</v>
       </c>
       <c r="N78">
         <f t="shared" si="14"/>
-        <v>5.2400000000000183E-2</v>
+        <v>7.2800000000000253E-2</v>
       </c>
       <c r="P78">
         <v>21.15</v>
@@ -27216,11 +27216,11 @@
         <v>2.1399999999999997</v>
       </c>
       <c r="H79">
-        <v>3.2160000000000001E-2</v>
+        <v>3.4349999999999999E-2</v>
       </c>
       <c r="I79">
         <f t="shared" si="13"/>
-        <v>0.31560000000000116</v>
+        <v>0.26040000000000102</v>
       </c>
       <c r="K79">
         <v>21.4</v>
@@ -27230,11 +27230,11 @@
         <v>2.1399999999999997</v>
       </c>
       <c r="M79">
-        <v>9.3000000000000005E-4</v>
+        <v>0</v>
       </c>
       <c r="N79">
         <f t="shared" si="14"/>
-        <v>2.1200000000000069E-2</v>
+        <v>1.8000000000000065E-2</v>
       </c>
       <c r="P79">
         <v>21.4</v>
@@ -27274,11 +27274,11 @@
         <v>2.165</v>
       </c>
       <c r="H80">
-        <v>2.7570000000000001E-2</v>
+        <v>2.8570000000000002E-2</v>
       </c>
       <c r="I80">
         <f t="shared" si="13"/>
-        <v>0.1835999999999974</v>
+        <v>0.2311999999999966</v>
       </c>
       <c r="K80">
         <v>21.65</v>
@@ -27292,7 +27292,7 @@
       </c>
       <c r="N80">
         <f t="shared" si="14"/>
-        <v>3.7199999999999477E-2</v>
+        <v>0</v>
       </c>
       <c r="P80">
         <v>21.65</v>
@@ -27332,11 +27332,11 @@
         <v>2.19</v>
       </c>
       <c r="H81">
-        <v>2.2450000000000001E-2</v>
+        <v>2.4729999999999999E-2</v>
       </c>
       <c r="I81">
         <f t="shared" si="13"/>
-        <v>0.2048000000000007</v>
+        <v>0.15360000000000068</v>
       </c>
       <c r="K81">
         <v>21.9</v>
@@ -27390,11 +27390,11 @@
         <v>2.2149999999999999</v>
       </c>
       <c r="H82">
-        <v>1.532E-2</v>
+        <v>1.9310000000000001E-2</v>
       </c>
       <c r="I82">
         <f t="shared" si="13"/>
-        <v>0.28520000000000106</v>
+        <v>0.21680000000000069</v>
       </c>
       <c r="K82">
         <v>22.15</v>
@@ -27448,11 +27448,11 @@
         <v>2.2399999999999998</v>
       </c>
       <c r="H83">
-        <v>1.108E-2</v>
+        <v>1.3559999999999999E-2</v>
       </c>
       <c r="I83">
         <f t="shared" si="13"/>
-        <v>0.16960000000000064</v>
+        <v>0.23000000000000087</v>
       </c>
       <c r="K83">
         <v>22.4</v>
@@ -27506,11 +27506,11 @@
         <v>2.2649999999999997</v>
       </c>
       <c r="H84">
-        <v>7.8499999999999993E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="I84">
         <f t="shared" si="13"/>
-        <v>0.12920000000000048</v>
+        <v>0.15840000000000057</v>
       </c>
       <c r="K84">
         <v>22.65</v>
@@ -27564,11 +27564,11 @@
         <v>2.29</v>
       </c>
       <c r="H85">
-        <v>5.1999999999999998E-3</v>
+        <v>7.1799999999999998E-3</v>
       </c>
       <c r="I85">
         <f t="shared" si="13"/>
-        <v>0.10599999999999847</v>
+        <v>9.6799999999998596E-2</v>
       </c>
       <c r="K85">
         <v>22.9</v>
@@ -27622,11 +27622,11 @@
         <v>2.3149999999999999</v>
       </c>
       <c r="H86">
-        <v>4.1900000000000001E-3</v>
+        <v>4.3699999999999998E-3</v>
       </c>
       <c r="I86">
         <f t="shared" si="13"/>
-        <v>4.040000000000013E-2</v>
+        <v>0.1124000000000004</v>
       </c>
       <c r="K86">
         <v>23.15</v>
@@ -27680,11 +27680,11 @@
         <v>2.34</v>
       </c>
       <c r="H87">
-        <v>4.0099999999999997E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="I87">
         <f t="shared" si="13"/>
-        <v>7.200000000000044E-3</v>
+        <v>1.0800000000000014E-2</v>
       </c>
       <c r="K87">
         <v>23.4</v>
@@ -27738,11 +27738,11 @@
         <v>2.3649999999999998</v>
       </c>
       <c r="H88">
-        <v>3.9100000000000003E-3</v>
+        <v>1.7099999999999999E-3</v>
       </c>
       <c r="I88">
         <f t="shared" si="13"/>
-        <v>3.9999999999999897E-3</v>
+        <v>9.5600000000000365E-2</v>
       </c>
       <c r="K88">
         <v>23.65</v>
@@ -27796,11 +27796,11 @@
         <v>2.3899999999999997</v>
       </c>
       <c r="H89">
-        <v>1.14E-3</v>
+        <v>1.6800000000000001E-3</v>
       </c>
       <c r="I89">
         <f t="shared" si="13"/>
-        <v>0.11080000000000041</v>
+        <v>1.1999999999999988E-3</v>
       </c>
       <c r="K89">
         <v>23.9</v>
@@ -27854,11 +27854,11 @@
         <v>2.415</v>
       </c>
       <c r="H90">
-        <v>1.1199999999999999E-3</v>
+        <v>8.8999999999999995E-4</v>
       </c>
       <c r="I90">
         <f t="shared" si="13"/>
-        <v>7.9999999999999071E-4</v>
+        <v>3.1599999999999559E-2</v>
       </c>
       <c r="K90">
         <v>24.15</v>
@@ -27912,11 +27912,11 @@
         <v>2.44</v>
       </c>
       <c r="H91">
-        <v>9.5E-4</v>
+        <v>0</v>
       </c>
       <c r="I91">
         <f t="shared" si="13"/>
-        <v>6.8000000000000204E-3</v>
+        <v>3.5600000000000125E-2</v>
       </c>
       <c r="K91">
         <v>24.4</v>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="I92">
         <f t="shared" si="13"/>
-        <v>3.8000000000000138E-2</v>
+        <v>0</v>
       </c>
       <c r="K92">
         <v>24.65</v>

--- a/tests/trj/Example_CEM/Example_output_files/PSD_Plot.xlsx
+++ b/tests/trj/Example_CEM/Example_output_files/PSD_Plot.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="477" documentId="8_{7149973D-7FBA-47E4-9186-8284705DD2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{008F84D0-CD8F-4543-8C11-BF50C147DCA0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12CB501-9D5F-4141-A117-3B2D7216ADD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GRO-GRO" sheetId="1" r:id="rId1"/>
